--- a/docs/01_overview/要件定義.xlsx
+++ b/docs/01_overview/要件定義.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ktakw\sg-mock-test-system\docs\01_overview\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2DC0468-B251-40F5-9C1B-D6AA56BC4346}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36DAA855-F265-40C7-92DD-D0E294E6A746}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{2761BF75-AFA8-428B-9FA1-0F0E7899F9CA}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{2761BF75-AFA8-428B-9FA1-0F0E7899F9CA}"/>
   </bookViews>
   <sheets>
     <sheet name="要件定義" sheetId="3" r:id="rId1"/>
-    <sheet name="要件定義メモ" sheetId="2" r:id="rId2"/>
+    <sheet name="機能一覧" sheetId="4" r:id="rId2"/>
+    <sheet name="要件定義メモ" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="361">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="595" uniqueCount="512">
   <si>
     <t>1 システム概要</t>
   </si>
@@ -1205,15 +1206,6 @@
     <t>現在、模擬試験はGoogleフォーム等を用いて実施されているが、以下の課題がある。</t>
   </si>
   <si>
-    <t>試験結果の管理が分散しており、効率が悪い</t>
-  </si>
-  <si>
-    <t>試験の開始・終了時間が自己申告であり、正確性に欠ける</t>
-  </si>
-  <si>
-    <t>問題管理や試験作成の柔軟性が低い</t>
-  </si>
-  <si>
     <t>これらの課題を解決するため、本システムを開発する。</t>
   </si>
   <si>
@@ -1223,301 +1215,798 @@
     <t>■ 講師</t>
   </si>
   <si>
+    <t>受講者の管理</t>
+  </si>
+  <si>
+    <t>試験結果の確認・分析</t>
+  </si>
+  <si>
+    <t>■ 受講者</t>
+  </si>
+  <si>
+    <t>模擬試験の受験</t>
+  </si>
+  <si>
+    <t>試験結果の確認</t>
+  </si>
+  <si>
+    <t>受験履歴の閲覧</t>
+  </si>
+  <si>
+    <t>4. システム範囲</t>
+  </si>
+  <si>
+    <t>本システムで提供する機能は以下の通りとする。</t>
+  </si>
+  <si>
+    <t>■ 共通機能</t>
+  </si>
+  <si>
+    <t>ログイン／ログアウト</t>
+  </si>
+  <si>
+    <t>■ 受講者機能</t>
+  </si>
+  <si>
+    <t>試験受験</t>
+  </si>
+  <si>
+    <t>試験結果確認</t>
+  </si>
+  <si>
+    <t>受験履歴閲覧</t>
+  </si>
+  <si>
+    <t>受験予定登録／報告</t>
+  </si>
+  <si>
+    <t>■ 講師機能</t>
+  </si>
+  <si>
+    <t>問題管理</t>
+  </si>
+  <si>
+    <t>試験管理</t>
+  </si>
+  <si>
+    <t>受講者管理</t>
+  </si>
+  <si>
+    <t>結果管理</t>
+  </si>
+  <si>
+    <t>受験承認</t>
+  </si>
+  <si>
+    <t>5. 機能要件</t>
+  </si>
+  <si>
+    <t>※詳細は機能一覧（A-01〜HIS-02）に準拠する。</t>
+  </si>
+  <si>
+    <t>■ アカウント機能</t>
+  </si>
+  <si>
+    <t>新規登録／更新／削除</t>
+  </si>
+  <si>
+    <t>■ 受験前機能（Preparation）</t>
+  </si>
+  <si>
+    <t>受験予定日選択</t>
+  </si>
+  <si>
+    <t>受験予定報告</t>
+  </si>
+  <si>
+    <t>講師による確認・承認</t>
+  </si>
+  <si>
+    <t>■ 受験機能（Execute）</t>
+  </si>
+  <si>
+    <t>時間管理</t>
+  </si>
+  <si>
+    <t>採点／結果表示</t>
+  </si>
+  <si>
+    <t>解説表示</t>
+  </si>
+  <si>
+    <t>受験完了報告</t>
+  </si>
+  <si>
+    <t>■ 受験後機能（History）</t>
+  </si>
+  <si>
+    <t>履歴閲覧（受講者）</t>
+  </si>
+  <si>
+    <t>履歴一覧（講師）</t>
+  </si>
+  <si>
+    <t>6. 非機能要件</t>
+  </si>
+  <si>
+    <t>■ 性能</t>
+  </si>
+  <si>
+    <t>同時接続ユーザー数：最大50人を想定</t>
+  </si>
+  <si>
+    <t>画面応答時間：3秒以内</t>
+  </si>
+  <si>
+    <t>■ 可用性</t>
+  </si>
+  <si>
+    <t>稼働率：99%以上</t>
+  </si>
+  <si>
+    <t>メンテナンス時間を除き常時利用可能</t>
+  </si>
+  <si>
+    <t>■ セキュリティ</t>
+  </si>
+  <si>
+    <t>パスワードはハッシュ化して保存</t>
+  </si>
+  <si>
+    <t>認証機能を実装し、不正アクセスを防止</t>
+  </si>
+  <si>
+    <t>HTTPS通信を使用</t>
+  </si>
+  <si>
+    <t>■ 操作性</t>
+  </si>
+  <si>
+    <t>初心者でも直感的に操作できるUI</t>
+  </si>
+  <si>
+    <t>スマートフォン・PC双方で利用可能</t>
+  </si>
+  <si>
+    <t>7. 画面要件</t>
+  </si>
+  <si>
+    <t>本システムは以下の画面で構成する。</t>
+  </si>
+  <si>
+    <t>ログイン画面</t>
+  </si>
+  <si>
+    <t>マイページ</t>
+  </si>
+  <si>
+    <t>試験一覧画面</t>
+  </si>
+  <si>
+    <t>試験画面</t>
+  </si>
+  <si>
+    <t>試験結果画面</t>
+  </si>
+  <si>
+    <t>履歴画面</t>
+  </si>
+  <si>
+    <t>管理者用画面（問題／試験／受講者管理）</t>
+  </si>
+  <si>
+    <t>8. データ要件</t>
+  </si>
+  <si>
+    <t>■ 主な管理データ</t>
+  </si>
+  <si>
+    <t>ユーザー情報</t>
+  </si>
+  <si>
+    <t>受験結果データ</t>
+  </si>
+  <si>
+    <t>受験履歴データ</t>
+  </si>
+  <si>
+    <t>9. 技術要件</t>
+  </si>
+  <si>
+    <t>■ フロントエンド</t>
+  </si>
+  <si>
+    <t>React</t>
+  </si>
+  <si>
+    <t>■ バックエンド</t>
+  </si>
+  <si>
+    <t>FastAPI</t>
+  </si>
+  <si>
+    <t>■ データベース</t>
+  </si>
+  <si>
+    <t>SQLite または PostgreSQL</t>
+  </si>
+  <si>
+    <t>■ 対象範囲</t>
+  </si>
+  <si>
+    <t>模擬試験システムの基本機能全般</t>
+  </si>
+  <si>
+    <t>■ 対象外</t>
+  </si>
+  <si>
+    <t>外部サービス連携（通知ツール等）</t>
+  </si>
+  <si>
+    <t>本番運用環境の構築</t>
+  </si>
+  <si>
+    <t>11. 成功基準</t>
+  </si>
+  <si>
+    <t>受講者が問題なく模擬試験を受験できること</t>
+  </si>
+  <si>
+    <t>講師が受験状況および結果を一元管理できること</t>
+  </si>
+  <si>
+    <t>試験運用の工数が削減されること</t>
+  </si>
+  <si>
+    <t>12. 競合分析</t>
+  </si>
+  <si>
+    <t>既存の類似サービスとして、オンライン試験ツールが存在するが、以下の点で課題がある。</t>
+  </si>
+  <si>
+    <t>カスタマイズ性が低い</t>
+  </si>
+  <si>
+    <t>13. 既存サービスの課題</t>
+  </si>
+  <si>
+    <t>受験管理が煩雑</t>
+  </si>
+  <si>
+    <t>試験時間の管理が不正確</t>
+  </si>
+  <si>
+    <t>結果分析機能が不足</t>
+  </si>
+  <si>
+    <t>14. 本アプリの独自性</t>
+  </si>
+  <si>
+    <t>研修に特化した設計</t>
+  </si>
+  <si>
+    <t>受験前〜受験後まで一貫管理</t>
+  </si>
+  <si>
+    <t>講師と受講者双方の操作性を考慮</t>
+  </si>
+  <si>
+    <t>15. 差別化まとめ</t>
+  </si>
+  <si>
+    <t>本システムは、模擬試験の運用に特化した機能を備え、既存サービスでは実現が難しい「受験管理の一元化」と「運用効率の向上」を実現する。</t>
+  </si>
+  <si>
+    <t>ログイン</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>　ログアウト</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>新規登録画面</t>
+    <rPh sb="0" eb="4">
+      <t>シンキトウロク</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ガメン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>問題データ(1問ごとの素材)</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>試験データ(問題をまとめた“セット（テスト）”)</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>10. 開発スコープ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>自社向けの機能が不足している</t>
+    <rPh sb="0" eb="2">
+      <t>ジシャ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ム</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
     <t>試験の作成・管理</t>
-  </si>
-  <si>
-    <t>受講者の管理</t>
-  </si>
-  <si>
-    <t>試験結果の確認・分析</t>
-  </si>
-  <si>
-    <t>■ 受講者</t>
-  </si>
-  <si>
-    <t>模擬試験の受験</t>
-  </si>
-  <si>
-    <t>試験結果の確認</t>
-  </si>
-  <si>
-    <t>受験履歴の閲覧</t>
-  </si>
-  <si>
-    <t>4. システム範囲</t>
-  </si>
-  <si>
-    <t>本システムで提供する機能は以下の通りとする。</t>
-  </si>
-  <si>
-    <t>■ 共通機能</t>
-  </si>
-  <si>
-    <t>ログイン／ログアウト</t>
-  </si>
-  <si>
-    <t>■ 受講者機能</t>
-  </si>
-  <si>
-    <t>試験受験</t>
-  </si>
-  <si>
-    <t>試験結果確認</t>
-  </si>
-  <si>
-    <t>受験履歴閲覧</t>
-  </si>
-  <si>
-    <t>受験予定登録／報告</t>
-  </si>
-  <si>
-    <t>■ 講師機能</t>
-  </si>
-  <si>
-    <t>問題管理</t>
-  </si>
-  <si>
-    <t>試験管理</t>
-  </si>
-  <si>
-    <t>受講者管理</t>
-  </si>
-  <si>
-    <t>結果管理</t>
-  </si>
-  <si>
-    <t>受験承認</t>
-  </si>
-  <si>
-    <t>5. 機能要件</t>
-  </si>
-  <si>
-    <t>※詳細は機能一覧（A-01〜HIS-02）に準拠する。</t>
-  </si>
-  <si>
-    <t>■ アカウント機能</t>
-  </si>
-  <si>
-    <t>新規登録／更新／削除</t>
-  </si>
-  <si>
-    <t>■ 受験前機能（Preparation）</t>
-  </si>
-  <si>
-    <t>受験予定日選択</t>
-  </si>
-  <si>
-    <t>受験予定報告</t>
-  </si>
-  <si>
-    <t>講師による確認・承認</t>
-  </si>
-  <si>
-    <t>■ 受験機能（Execute）</t>
-  </si>
-  <si>
-    <t>時間管理</t>
-  </si>
-  <si>
-    <t>採点／結果表示</t>
-  </si>
-  <si>
-    <t>解説表示</t>
-  </si>
-  <si>
-    <t>受験完了報告</t>
-  </si>
-  <si>
-    <t>■ 受験後機能（History）</t>
-  </si>
-  <si>
-    <t>履歴閲覧（受講者）</t>
-  </si>
-  <si>
-    <t>履歴一覧（講師）</t>
-  </si>
-  <si>
-    <t>6. 非機能要件</t>
-  </si>
-  <si>
-    <t>■ 性能</t>
-  </si>
-  <si>
-    <t>同時接続ユーザー数：最大50人を想定</t>
-  </si>
-  <si>
-    <t>画面応答時間：3秒以内</t>
-  </si>
-  <si>
-    <t>■ 可用性</t>
-  </si>
-  <si>
-    <t>稼働率：99%以上</t>
-  </si>
-  <si>
-    <t>メンテナンス時間を除き常時利用可能</t>
-  </si>
-  <si>
-    <t>■ セキュリティ</t>
-  </si>
-  <si>
-    <t>パスワードはハッシュ化して保存</t>
-  </si>
-  <si>
-    <t>認証機能を実装し、不正アクセスを防止</t>
-  </si>
-  <si>
-    <t>HTTPS通信を使用</t>
-  </si>
-  <si>
-    <t>■ 操作性</t>
-  </si>
-  <si>
-    <t>初心者でも直感的に操作できるUI</t>
-  </si>
-  <si>
-    <t>スマートフォン・PC双方で利用可能</t>
-  </si>
-  <si>
-    <t>7. 画面要件</t>
-  </si>
-  <si>
-    <t>本システムは以下の画面で構成する。</t>
-  </si>
-  <si>
-    <t>ログイン画面</t>
-  </si>
-  <si>
-    <t>マイページ</t>
-  </si>
-  <si>
-    <t>試験一覧画面</t>
-  </si>
-  <si>
-    <t>試験画面</t>
-  </si>
-  <si>
-    <t>試験結果画面</t>
-  </si>
-  <si>
-    <t>履歴画面</t>
-  </si>
-  <si>
-    <t>管理者用画面（問題／試験／受講者管理）</t>
-  </si>
-  <si>
-    <t>8. データ要件</t>
-  </si>
-  <si>
-    <t>■ 主な管理データ</t>
-  </si>
-  <si>
-    <t>ユーザー情報</t>
-  </si>
-  <si>
-    <t>問題データ</t>
-  </si>
-  <si>
-    <t>試験データ</t>
-  </si>
-  <si>
-    <t>受験結果データ</t>
-  </si>
-  <si>
-    <t>受験履歴データ</t>
-  </si>
-  <si>
-    <t>9. 技術要件</t>
-  </si>
-  <si>
-    <t>■ フロントエンド</t>
-  </si>
-  <si>
-    <t>React</t>
-  </si>
-  <si>
-    <t>■ バックエンド</t>
-  </si>
-  <si>
-    <t>FastAPI</t>
-  </si>
-  <si>
-    <t>■ データベース</t>
-  </si>
-  <si>
-    <t>SQLite または PostgreSQL</t>
-  </si>
-  <si>
-    <t>10. 開発スコープ</t>
-  </si>
-  <si>
-    <t>■ 対象範囲</t>
-  </si>
-  <si>
-    <t>模擬試験システムの基本機能全般</t>
-  </si>
-  <si>
-    <t>■ 対象外</t>
-  </si>
-  <si>
-    <t>外部サービス連携（通知ツール等）</t>
-  </si>
-  <si>
-    <t>本番運用環境の構築</t>
-  </si>
-  <si>
-    <t>11. 成功基準</t>
-  </si>
-  <si>
-    <t>受講者が問題なく模擬試験を受験できること</t>
-  </si>
-  <si>
-    <t>講師が受験状況および結果を一元管理できること</t>
-  </si>
-  <si>
-    <t>試験運用の工数が削減されること</t>
-  </si>
-  <si>
-    <t>12. 競合分析</t>
-  </si>
-  <si>
-    <t>既存の類似サービスとして、オンライン試験ツールが存在するが、以下の点で課題がある。</t>
-  </si>
-  <si>
-    <t>カスタマイズ性が低い</t>
-  </si>
-  <si>
-    <t>研修特化の機能が不足している</t>
-  </si>
-  <si>
-    <t>13. 既存サービスの課題</t>
-  </si>
-  <si>
-    <t>受験管理が煩雑</t>
-  </si>
-  <si>
-    <t>試験時間の管理が不正確</t>
-  </si>
-  <si>
-    <t>結果分析機能が不足</t>
-  </si>
-  <si>
-    <t>14. 本アプリの独自性</t>
-  </si>
-  <si>
-    <t>研修に特化した設計</t>
-  </si>
-  <si>
-    <t>受験前〜受験後まで一貫管理</t>
-  </si>
-  <si>
-    <t>講師と受講者双方の操作性を考慮</t>
-  </si>
-  <si>
-    <t>15. 差別化まとめ</t>
-  </si>
-  <si>
-    <t>本システムは、模擬試験の運用に特化した機能を備え、既存サービスでは実現が難しい「受験管理の一元化」と「運用効率の向上」を実現する。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>・試験結果の管理が分散しており、効率が悪い</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>・試験の開始・終了時間が自己申告であり、正確性に欠ける</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>・問題管理や試験作成の柔軟性が低い</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>機能ID</t>
+  </si>
+  <si>
+    <t>機能名</t>
+  </si>
+  <si>
+    <t>概要</t>
+  </si>
+  <si>
+    <t>入力</t>
+  </si>
+  <si>
+    <t>出力</t>
+  </si>
+  <si>
+    <t>対象ユーザー</t>
+  </si>
+  <si>
+    <t>A-01</t>
+  </si>
+  <si>
+    <t>ログイン機能</t>
+  </si>
+  <si>
+    <t>ユーザーがログインする</t>
+  </si>
+  <si>
+    <t>メールアドレス、パスワード</t>
+  </si>
+  <si>
+    <t>トップ画面、エラーメッセージ</t>
+  </si>
+  <si>
+    <t>全員</t>
+  </si>
+  <si>
+    <t>A-02</t>
+  </si>
+  <si>
+    <t>ログアウト機能</t>
+  </si>
+  <si>
+    <t>ユーザーがログアウトする</t>
+  </si>
+  <si>
+    <t>ログアウト操作</t>
+  </si>
+  <si>
+    <t>A-03</t>
+  </si>
+  <si>
+    <t>新規登録機能</t>
+  </si>
+  <si>
+    <t>ユーザーがアカウント登録する</t>
+  </si>
+  <si>
+    <t>名前、メール、パスワード</t>
+  </si>
+  <si>
+    <t>ログイン画面、登録完了メッセージ</t>
+  </si>
+  <si>
+    <t>A-04</t>
+  </si>
+  <si>
+    <t>アカウント削除機能</t>
+  </si>
+  <si>
+    <t>講師がユーザーを削除する</t>
+  </si>
+  <si>
+    <t>対象ユーザー選択</t>
+  </si>
+  <si>
+    <t>一覧画面、削除完了メッセージ</t>
+  </si>
+  <si>
+    <t>講師</t>
+  </si>
+  <si>
+    <t>A-05</t>
+  </si>
+  <si>
+    <t>アカウント更新機能</t>
+  </si>
+  <si>
+    <t>ユーザー情報を更新する</t>
+  </si>
+  <si>
+    <t>名前、メール、パスワード等</t>
+  </si>
+  <si>
+    <t>PRE-01</t>
+  </si>
+  <si>
+    <t>受験予定日選択機能</t>
+  </si>
+  <si>
+    <t>受験予定日時を選択する</t>
+  </si>
+  <si>
+    <t>受験日、開始時間</t>
+  </si>
+  <si>
+    <t>登録完了画面</t>
+  </si>
+  <si>
+    <t>受講者</t>
+  </si>
+  <si>
+    <t>PRE-02</t>
+  </si>
+  <si>
+    <t>受験予定日報告機能</t>
+  </si>
+  <si>
+    <t>選択した予定を講師に報告</t>
+  </si>
+  <si>
+    <t>受験予定日時</t>
+  </si>
+  <si>
+    <t>報告完了メッセージ</t>
+  </si>
+  <si>
+    <t>PRE-03</t>
+  </si>
+  <si>
+    <t>受験予定一覧表示機能</t>
+  </si>
+  <si>
+    <t>受講者の予定一覧を表示</t>
+  </si>
+  <si>
+    <t>なし</t>
+  </si>
+  <si>
+    <t>一覧表示</t>
+  </si>
+  <si>
+    <t>PRE-04</t>
+  </si>
+  <si>
+    <t>受験予定受理機能</t>
+  </si>
+  <si>
+    <t>講師が予定を承認</t>
+  </si>
+  <si>
+    <t>対象データ選択</t>
+  </si>
+  <si>
+    <t>受理完了メッセージ</t>
+  </si>
+  <si>
+    <t>EXE-01</t>
+  </si>
+  <si>
+    <t>模擬試験受験機能</t>
+  </si>
+  <si>
+    <t>試験を受験する</t>
+  </si>
+  <si>
+    <t>開始操作</t>
+  </si>
+  <si>
+    <t>問題画面</t>
+  </si>
+  <si>
+    <t>EXE-02</t>
+  </si>
+  <si>
+    <t>試験時間管理機能</t>
+  </si>
+  <si>
+    <t>試験時間を管理する</t>
+  </si>
+  <si>
+    <t>開始時刻</t>
+  </si>
+  <si>
+    <t>タイマー表示</t>
+  </si>
+  <si>
+    <t>EXE-03</t>
+  </si>
+  <si>
+    <t>試験結果表示機能</t>
+  </si>
+  <si>
+    <t>結果を表示する</t>
+  </si>
+  <si>
+    <t>得点、正誤</t>
+  </si>
+  <si>
+    <t>EXE-04</t>
+  </si>
+  <si>
+    <t>解答表示機能</t>
+  </si>
+  <si>
+    <t>解答と解説を表示する</t>
+  </si>
+  <si>
+    <t>正解、解説</t>
+  </si>
+  <si>
+    <t>EXE-05</t>
+  </si>
+  <si>
+    <t>試験完了報告機能</t>
+  </si>
+  <si>
+    <t>試験完了を報告する</t>
+  </si>
+  <si>
+    <t>報告操作</t>
+  </si>
+  <si>
+    <t>完了メッセージ</t>
+  </si>
+  <si>
+    <t>EXE-06</t>
+  </si>
+  <si>
+    <t>試験結果一覧表示機能</t>
+  </si>
+  <si>
+    <t>結果一覧を表示する</t>
+  </si>
+  <si>
+    <t>EXE-07</t>
+  </si>
+  <si>
+    <t>試験完了承認機能</t>
+  </si>
+  <si>
+    <t>完了報告を承認する</t>
+  </si>
+  <si>
+    <t>対象選択</t>
+  </si>
+  <si>
+    <t>承認メッセージ</t>
+  </si>
+  <si>
+    <t>HIS-01</t>
+  </si>
+  <si>
+    <t>履歴保存・閲覧機能</t>
+  </si>
+  <si>
+    <t>受験履歴を保存・表示</t>
+  </si>
+  <si>
+    <t>履歴一覧</t>
+  </si>
+  <si>
+    <t>HIS-02</t>
+  </si>
+  <si>
+    <t>履歴一覧表示機能</t>
+  </si>
+  <si>
+    <t>全受講者の履歴を表示</t>
+  </si>
+  <si>
+    <t>検索条件</t>
+  </si>
+  <si>
+    <t>処理内容</t>
+  </si>
+  <si>
+    <t>条件・制約</t>
+  </si>
+  <si>
+    <t>備考</t>
+  </si>
+  <si>
+    <t>入力値チェック→ユーザー取得→パスワード照合→セッション生成</t>
+  </si>
+  <si>
+    <t>未入力不可、認証失敗時エラー</t>
+  </si>
+  <si>
+    <t>セッション管理あり</t>
+  </si>
+  <si>
+    <t>セッション無効化→認証情報削除</t>
+  </si>
+  <si>
+    <t>ログイン状態のみ実行可能</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>入力チェック→メール重複確認→パスワードハッシュ化→DB登録</t>
+  </si>
+  <si>
+    <t>メール重複不可、形式チェック必須</t>
+  </si>
+  <si>
+    <t>パスワードはハッシュ化</t>
+  </si>
+  <si>
+    <t>対象ユーザー確認→DB削除→関連データ処理</t>
+  </si>
+  <si>
+    <t>講師のみ実行可能、存在しないユーザー不可</t>
+  </si>
+  <si>
+    <t>論理削除推奨</t>
+  </si>
+  <si>
+    <t>入力チェック→ユーザー確認→重複チェック→更新処理</t>
+  </si>
+  <si>
+    <t>本人または講師のみ、メール重複不可</t>
+  </si>
+  <si>
+    <t>パスワード変更時ハッシュ化</t>
+  </si>
+  <si>
+    <t>入力チェック→過去日時確認→重複確認→DB登録</t>
+  </si>
+  <si>
+    <t>過去日時不可、重複不可</t>
+  </si>
+  <si>
+    <t>時間制限あり</t>
+  </si>
+  <si>
+    <t>登録済み確認→報告登録→ステータス更新</t>
+  </si>
+  <si>
+    <t>未登録は報告不可、重複報告不可</t>
+  </si>
+  <si>
+    <t>ステータス管理あり</t>
+  </si>
+  <si>
+    <t>DBから予定取得→一覧整形→表示</t>
+  </si>
+  <si>
+    <t>講師のみ閲覧可能</t>
+  </si>
+  <si>
+    <t>データなし時は表示制御</t>
+  </si>
+  <si>
+    <t>報告済確認→ステータス更新→通知登録</t>
+  </si>
+  <si>
+    <t>未報告不可、再承認不可</t>
+  </si>
+  <si>
+    <t>通知機能あり</t>
+  </si>
+  <si>
+    <t>受験可否確認→問題取得→セッション開始</t>
+  </si>
+  <si>
+    <t>受験時間外不可、再受験制御あり</t>
+  </si>
+  <si>
+    <t>状態管理必要</t>
+  </si>
+  <si>
+    <t>開始時刻記録→終了時刻算出→タイマー更新→自動終了</t>
+  </si>
+  <si>
+    <t>制限時間超過で終了</t>
+  </si>
+  <si>
+    <t>サーバー時間基準</t>
+  </si>
+  <si>
+    <t>回答採点→結果算出→表示</t>
+  </si>
+  <si>
+    <t>受験完了後のみ表示</t>
+  </si>
+  <si>
+    <t>合否判定は任意</t>
+  </si>
+  <si>
+    <t>問題・正解取得→回答照合→解説表示</t>
+  </si>
+  <si>
+    <t>未受験不可</t>
+  </si>
+  <si>
+    <t>完了確認→ステータス更新→報告登録</t>
+  </si>
+  <si>
+    <t>未完了不可</t>
+  </si>
+  <si>
+    <t>DB取得→一覧整形</t>
+  </si>
+  <si>
+    <t>報告確認→ステータス更新→通知</t>
+  </si>
+  <si>
+    <t>通知あり</t>
+  </si>
+  <si>
+    <t>試験完了時保存→履歴取得→表示</t>
+  </si>
+  <si>
+    <t>本人のみ閲覧可能</t>
+  </si>
+  <si>
+    <t>データなし時表示制御</t>
+  </si>
+  <si>
+    <t>DB取得→検索→一覧表示</t>
+  </si>
+  <si>
+    <t>フィルタ可能</t>
+  </si>
+  <si>
+    <t>機能一覧</t>
+    <rPh sb="0" eb="4">
+      <t>キノウイチラン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>C</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>R</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>U</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>D</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>CRUD要素</t>
+    <rPh sb="4" eb="6">
+      <t>ヨウソ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
   </si>
 </sst>
 </file>
@@ -1576,20 +2065,47 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -1598,7 +2114,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1620,11 +2136,23 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1644,75 +2172,6 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>533400</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>15240</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>335280</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>30480</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="3" name="四角形: 角を丸くする 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CF550D32-0BE9-ABC2-0A8C-455A0779C023}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="533400" y="243840"/>
-          <a:ext cx="3154680" cy="838200"/>
-        </a:xfrm>
-        <a:prstGeom prst="roundRect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-            <a:t>まだ未完成</a:t>
-          </a:r>
-          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -2953,652 +3412,1245 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB02E399-8693-4826-BC98-B6B643279500}">
-  <dimension ref="B2:B207"/>
+  <dimension ref="B2:B209"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="2" max="2" width="8.796875" style="7"/>
+  </cols>
   <sheetData>
     <row r="2" spans="2:2" ht="28.8" x14ac:dyDescent="0.45">
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="8" t="s">
         <v>251</v>
       </c>
     </row>
     <row r="4" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B4" t="s">
+      <c r="B4" s="7" t="s">
         <v>252</v>
       </c>
     </row>
     <row r="5" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>253</v>
       </c>
     </row>
     <row r="9" spans="2:2" ht="28.8" x14ac:dyDescent="0.45">
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="8" t="s">
         <v>254</v>
       </c>
     </row>
     <row r="11" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B11" t="s">
+      <c r="B11" s="7" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="12" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B12" s="5"/>
-    </row>
     <row r="13" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="7" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="14" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B14" s="7" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="15" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B15" s="7" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B17" s="7" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="14" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B14" s="5" t="s">
+    <row r="21" spans="2:2" ht="28.8" x14ac:dyDescent="0.45">
+      <c r="B21" s="8" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="15" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B15" s="5" t="s">
+    <row r="23" spans="2:2" ht="22.2" x14ac:dyDescent="0.45">
+      <c r="B23" s="9" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B17" t="s">
+    <row r="25" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B25" s="7" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="26" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B26" s="7" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="21" spans="2:2" ht="28.8" x14ac:dyDescent="0.45">
-      <c r="B21" s="7" t="s">
+    <row r="27" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B27" s="7" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="23" spans="2:2" ht="22.2" x14ac:dyDescent="0.45">
-      <c r="B23" s="8" t="s">
+    <row r="29" spans="2:2" ht="22.2" x14ac:dyDescent="0.45">
+      <c r="B29" s="9" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="24" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B24" s="5"/>
-    </row>
-    <row r="25" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B25" s="5" t="s">
+    <row r="31" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B31" s="7" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="26" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B26" s="5" t="s">
+    <row r="32" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B32" s="7" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="27" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B27" s="5" t="s">
+    <row r="33" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B33" s="7" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="29" spans="2:2" ht="22.2" x14ac:dyDescent="0.45">
-      <c r="B29" s="8" t="s">
+    <row r="37" spans="2:2" ht="28.8" x14ac:dyDescent="0.45">
+      <c r="B37" s="8" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="30" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B30" s="5"/>
-    </row>
-    <row r="31" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B31" s="5" t="s">
+    <row r="39" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B39" s="7" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="32" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B32" s="5" t="s">
+    <row r="41" spans="2:2" ht="22.2" x14ac:dyDescent="0.45">
+      <c r="B41" s="9" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="33" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B33" s="5" t="s">
+    <row r="43" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B43" s="7" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="44" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B44" s="7" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="46" spans="2:2" ht="22.2" x14ac:dyDescent="0.45">
+      <c r="B46" s="9" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="48" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B48" s="7" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="49" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B49" s="7" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="50" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B50" s="7" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="51" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B51" s="7" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="53" spans="2:2" ht="22.2" x14ac:dyDescent="0.45">
+      <c r="B53" s="9" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="55" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B55" s="7" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="56" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B56" s="7" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="57" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B57" s="7" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="58" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B58" s="7" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="59" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B59" s="7" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="63" spans="2:2" ht="28.8" x14ac:dyDescent="0.45">
+      <c r="B63" s="8" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="65" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B65" s="7" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="67" spans="2:2" ht="22.2" x14ac:dyDescent="0.45">
+      <c r="B67" s="9" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="69" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B69" s="7" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="37" spans="2:2" ht="28.8" x14ac:dyDescent="0.45">
-      <c r="B37" s="7" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="39" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B39" t="s">
+    <row r="70" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B70" s="7" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="72" spans="2:2" ht="22.2" x14ac:dyDescent="0.45">
+      <c r="B72" s="9" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="74" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B74" s="7" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="75" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B75" s="7" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="76" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B76" s="7" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="78" spans="2:2" ht="22.2" x14ac:dyDescent="0.45">
+      <c r="B78" s="9" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="80" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B80" s="7" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="41" spans="2:2" ht="22.2" x14ac:dyDescent="0.45">
-      <c r="B41" s="8" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="42" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B42" s="5"/>
-    </row>
-    <row r="43" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B43" s="5" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="45" spans="2:2" ht="22.2" x14ac:dyDescent="0.45">
-      <c r="B45" s="8" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="46" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B46" s="5"/>
-    </row>
-    <row r="47" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B47" s="5" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="48" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B48" s="5" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="49" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B49" s="5" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="50" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B50" s="5" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="52" spans="2:2" ht="22.2" x14ac:dyDescent="0.45">
-      <c r="B52" s="8" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="53" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B53" s="5"/>
-    </row>
-    <row r="54" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B54" s="5" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="55" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B55" s="5" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="56" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B56" s="5" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="57" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B57" s="5" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="58" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B58" s="5" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="62" spans="2:2" ht="28.8" x14ac:dyDescent="0.45">
-      <c r="B62" s="7" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="64" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B64" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="66" spans="2:2" ht="22.2" x14ac:dyDescent="0.45">
-      <c r="B66" s="8" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="67" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B67" s="5"/>
-    </row>
-    <row r="68" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B68" s="5" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="69" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B69" s="5" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="71" spans="2:2" ht="22.2" x14ac:dyDescent="0.45">
-      <c r="B71" s="8" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="72" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B72" s="5"/>
-    </row>
-    <row r="73" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B73" s="5" t="s">
+    <row r="81" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B81" s="7" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="74" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B74" s="5" t="s">
+    <row r="82" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B82" s="7" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="75" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B75" s="5" t="s">
+    <row r="83" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B83" s="7" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="77" spans="2:2" ht="22.2" x14ac:dyDescent="0.45">
-      <c r="B77" s="8" t="s">
+    <row r="84" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B84" s="7" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="78" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B78" s="5"/>
-    </row>
-    <row r="79" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B79" s="5" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="80" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B80" s="5" t="s">
+    <row r="86" spans="2:2" ht="22.2" x14ac:dyDescent="0.45">
+      <c r="B86" s="9" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="81" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B81" s="5" t="s">
+    <row r="88" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B88" s="7" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="82" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B82" s="5" t="s">
+    <row r="89" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B89" s="7" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="83" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B83" s="5" t="s">
+    <row r="93" spans="2:2" ht="28.8" x14ac:dyDescent="0.45">
+      <c r="B93" s="8" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="85" spans="2:2" ht="22.2" x14ac:dyDescent="0.45">
-      <c r="B85" s="8" t="s">
+    <row r="95" spans="2:2" ht="22.2" x14ac:dyDescent="0.45">
+      <c r="B95" s="9" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="86" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B86" s="5"/>
-    </row>
-    <row r="87" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B87" s="5" t="s">
+    <row r="97" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B97" s="7" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="88" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B88" s="5" t="s">
+    <row r="98" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B98" s="7" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="92" spans="2:2" ht="28.8" x14ac:dyDescent="0.45">
-      <c r="B92" s="7" t="s">
+    <row r="100" spans="2:2" ht="22.2" x14ac:dyDescent="0.45">
+      <c r="B100" s="9" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="94" spans="2:2" ht="22.2" x14ac:dyDescent="0.45">
-      <c r="B94" s="8" t="s">
+    <row r="102" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B102" s="7" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="95" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B95" s="5"/>
-    </row>
-    <row r="96" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B96" s="5" t="s">
+    <row r="103" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B103" s="7" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="97" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B97" s="5" t="s">
+    <row r="105" spans="2:2" ht="22.2" x14ac:dyDescent="0.45">
+      <c r="B105" s="9" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="99" spans="2:2" ht="22.2" x14ac:dyDescent="0.45">
-      <c r="B99" s="8" t="s">
+    <row r="107" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B107" s="7" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="100" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B100" s="5"/>
-    </row>
-    <row r="101" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B101" s="5" t="s">
+    <row r="108" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B108" s="7" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="102" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B102" s="5" t="s">
+    <row r="109" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B109" s="7" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="104" spans="2:2" ht="22.2" x14ac:dyDescent="0.45">
-      <c r="B104" s="8" t="s">
+    <row r="111" spans="2:2" ht="22.2" x14ac:dyDescent="0.45">
+      <c r="B111" s="9" t="s">
         <v>307</v>
       </c>
     </row>
-    <row r="105" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B105" s="5"/>
-    </row>
-    <row r="106" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B106" s="5" t="s">
+    <row r="113" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B113" s="7" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="107" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B107" s="5" t="s">
+    <row r="114" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B114" s="7" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="108" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B108" s="5" t="s">
+    <row r="118" spans="2:2" ht="28.8" x14ac:dyDescent="0.45">
+      <c r="B118" s="8" t="s">
         <v>310</v>
       </c>
     </row>
-    <row r="110" spans="2:2" ht="22.2" x14ac:dyDescent="0.45">
-      <c r="B110" s="8" t="s">
+    <row r="120" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B120" s="7" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="111" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B111" s="5"/>
-    </row>
-    <row r="112" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B112" s="5" t="s">
+    <row r="122" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B122" s="7" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="113" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B113" s="5" t="s">
+    <row r="123" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B123" s="7" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="124" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B124" s="7" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="117" spans="2:2" ht="28.8" x14ac:dyDescent="0.45">
-      <c r="B117" s="7" t="s">
+    <row r="125" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B125" s="7" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="119" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B119" t="s">
+    <row r="126" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B126" s="7" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="120" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B120" s="5"/>
-    </row>
-    <row r="121" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B121" s="5" t="s">
+    <row r="127" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B127" s="7" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="122" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B122" s="5" t="s">
+    <row r="128" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B128" s="7" t="s">
         <v>317</v>
       </c>
     </row>
-    <row r="123" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B123" s="5" t="s">
+    <row r="129" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B129" s="7" t="s">
         <v>318</v>
       </c>
     </row>
-    <row r="124" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B124" s="5" t="s">
+    <row r="133" spans="2:2" ht="28.8" x14ac:dyDescent="0.45">
+      <c r="B133" s="8" t="s">
         <v>319</v>
       </c>
     </row>
-    <row r="125" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B125" s="5" t="s">
+    <row r="135" spans="2:2" ht="22.2" x14ac:dyDescent="0.45">
+      <c r="B135" s="9" t="s">
         <v>320</v>
       </c>
     </row>
-    <row r="126" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B126" s="5" t="s">
+    <row r="137" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B137" s="7" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="127" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B127" s="5" t="s">
+    <row r="138" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B138" s="7" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="139" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B139" s="7" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="140" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B140" s="7" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="131" spans="2:2" ht="28.8" x14ac:dyDescent="0.45">
-      <c r="B131" s="7" t="s">
+    <row r="141" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B141" s="7" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="133" spans="2:2" ht="22.2" x14ac:dyDescent="0.45">
-      <c r="B133" s="8" t="s">
+    <row r="145" spans="2:2" ht="28.8" x14ac:dyDescent="0.45">
+      <c r="B145" s="8" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="134" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B134" s="5"/>
-    </row>
-    <row r="135" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B135" s="5" t="s">
+    <row r="147" spans="2:2" ht="22.2" x14ac:dyDescent="0.45">
+      <c r="B147" s="9" t="s">
         <v>325</v>
       </c>
     </row>
-    <row r="136" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B136" s="5" t="s">
+    <row r="149" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B149" s="7" t="s">
         <v>326</v>
       </c>
     </row>
-    <row r="137" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B137" s="5" t="s">
+    <row r="151" spans="2:2" ht="22.2" x14ac:dyDescent="0.45">
+      <c r="B151" s="9" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="138" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B138" s="5" t="s">
+    <row r="153" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B153" s="7" t="s">
         <v>328</v>
       </c>
     </row>
-    <row r="139" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B139" s="5" t="s">
+    <row r="155" spans="2:2" ht="22.2" x14ac:dyDescent="0.45">
+      <c r="B155" s="9" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="143" spans="2:2" ht="28.8" x14ac:dyDescent="0.45">
-      <c r="B143" s="7" t="s">
+    <row r="157" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B157" s="7" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="145" spans="2:2" ht="22.2" x14ac:dyDescent="0.45">
-      <c r="B145" s="8" t="s">
+    <row r="161" spans="2:2" ht="28.8" x14ac:dyDescent="0.45">
+      <c r="B161" s="8" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="163" spans="2:2" ht="22.2" x14ac:dyDescent="0.45">
+      <c r="B163" s="9" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="146" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B146" s="5"/>
-    </row>
-    <row r="147" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B147" s="5" t="s">
+    <row r="165" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B165" s="7" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="149" spans="2:2" ht="22.2" x14ac:dyDescent="0.45">
-      <c r="B149" s="8" t="s">
+    <row r="167" spans="2:2" ht="22.2" x14ac:dyDescent="0.45">
+      <c r="B167" s="9" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="150" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B150" s="5"/>
-    </row>
-    <row r="151" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B151" s="5" t="s">
+    <row r="169" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B169" s="7" t="s">
         <v>334</v>
       </c>
     </row>
-    <row r="153" spans="2:2" ht="22.2" x14ac:dyDescent="0.45">
-      <c r="B153" s="8" t="s">
+    <row r="170" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B170" s="7" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="154" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B154" s="5"/>
-    </row>
-    <row r="155" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B155" s="5" t="s">
+    <row r="174" spans="2:2" ht="28.8" x14ac:dyDescent="0.45">
+      <c r="B174" s="8" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="159" spans="2:2" ht="28.8" x14ac:dyDescent="0.45">
-      <c r="B159" s="7" t="s">
+    <row r="176" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B176" s="7" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="161" spans="2:2" ht="22.2" x14ac:dyDescent="0.45">
-      <c r="B161" s="8" t="s">
+    <row r="177" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B177" s="7" t="s">
         <v>338</v>
       </c>
     </row>
-    <row r="162" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B162" s="5"/>
-    </row>
-    <row r="163" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B163" s="5" t="s">
+    <row r="178" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B178" s="7" t="s">
         <v>339</v>
       </c>
     </row>
-    <row r="165" spans="2:2" ht="22.2" x14ac:dyDescent="0.45">
-      <c r="B165" s="8" t="s">
+    <row r="182" spans="2:2" ht="28.8" x14ac:dyDescent="0.45">
+      <c r="B182" s="8" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="166" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B166" s="5"/>
-    </row>
-    <row r="167" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B167" s="5" t="s">
+    <row r="184" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B184" s="7" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="168" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B168" s="5" t="s">
+    <row r="186" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B186" s="7" t="s">
         <v>342</v>
       </c>
     </row>
-    <row r="172" spans="2:2" ht="28.8" x14ac:dyDescent="0.45">
-      <c r="B172" s="7" t="s">
+    <row r="187" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B187" s="7" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="191" spans="2:2" ht="28.8" x14ac:dyDescent="0.45">
+      <c r="B191" s="8" t="s">
         <v>343</v>
       </c>
     </row>
-    <row r="173" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B173" s="5"/>
-    </row>
-    <row r="174" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B174" s="5" t="s">
+    <row r="193" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B193" s="7" t="s">
         <v>344</v>
       </c>
     </row>
-    <row r="175" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B175" s="5" t="s">
+    <row r="194" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B194" s="7" t="s">
         <v>345</v>
       </c>
     </row>
-    <row r="176" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B176" s="5" t="s">
+    <row r="195" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B195" s="7" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="180" spans="2:2" ht="28.8" x14ac:dyDescent="0.45">
-      <c r="B180" s="7" t="s">
+    <row r="199" spans="2:2" ht="28.8" x14ac:dyDescent="0.45">
+      <c r="B199" s="8" t="s">
         <v>347</v>
       </c>
     </row>
-    <row r="182" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B182" t="s">
+    <row r="201" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B201" s="7" t="s">
         <v>348</v>
       </c>
     </row>
-    <row r="183" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B183" s="5"/>
-    </row>
-    <row r="184" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B184" s="5" t="s">
+    <row r="202" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B202" s="7" t="s">
         <v>349</v>
       </c>
     </row>
-    <row r="185" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B185" s="5" t="s">
+    <row r="203" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B203" s="7" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="189" spans="2:2" ht="28.8" x14ac:dyDescent="0.45">
-      <c r="B189" s="7" t="s">
+    <row r="207" spans="2:2" ht="28.8" x14ac:dyDescent="0.45">
+      <c r="B207" s="8" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="190" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B190" s="5"/>
-    </row>
-    <row r="191" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B191" s="5" t="s">
+    <row r="209" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B209" s="7" t="s">
         <v>352</v>
-      </c>
-    </row>
-    <row r="192" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B192" s="5" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="193" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B193" s="5" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="197" spans="2:2" ht="28.8" x14ac:dyDescent="0.45">
-      <c r="B197" s="7" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="198" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B198" s="5"/>
-    </row>
-    <row r="199" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B199" s="5" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="200" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B200" s="5" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="201" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B201" s="5" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="205" spans="2:2" ht="28.8" x14ac:dyDescent="0.45">
-      <c r="B205" s="7" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="207" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B207" t="s">
-        <v>360</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A0697D5-EC04-49BC-B882-B72733D97B34}">
+  <dimension ref="B2:K24"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.3984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="27.59765625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="33.69921875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="63" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="42.09765625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="27.59765625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="B2" s="12" t="s">
+        <v>506</v>
+      </c>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="12"/>
+      <c r="G2" s="12"/>
+      <c r="H2" s="12"/>
+      <c r="I2" s="12"/>
+      <c r="J2" s="12"/>
+      <c r="K2" s="12"/>
+    </row>
+    <row r="3" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="B3" s="11" t="s">
+        <v>364</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>365</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>366</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>367</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>368</v>
+      </c>
+      <c r="G3" s="11" t="s">
+        <v>455</v>
+      </c>
+      <c r="H3" s="11" t="s">
+        <v>456</v>
+      </c>
+      <c r="I3" s="11" t="s">
+        <v>457</v>
+      </c>
+      <c r="J3" s="11" t="s">
+        <v>369</v>
+      </c>
+      <c r="K3" s="11" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="4" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="B4" s="10" t="s">
+        <v>370</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>371</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>372</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>373</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>374</v>
+      </c>
+      <c r="G4" s="10" t="s">
+        <v>458</v>
+      </c>
+      <c r="H4" s="10" t="s">
+        <v>459</v>
+      </c>
+      <c r="I4" s="10" t="s">
+        <v>460</v>
+      </c>
+      <c r="J4" s="10" t="s">
+        <v>375</v>
+      </c>
+      <c r="K4" s="10" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="5" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="B5" s="10" t="s">
+        <v>376</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>377</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>378</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>379</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>312</v>
+      </c>
+      <c r="G5" s="10" t="s">
+        <v>461</v>
+      </c>
+      <c r="H5" s="10" t="s">
+        <v>462</v>
+      </c>
+      <c r="I5" s="10" t="s">
+        <v>463</v>
+      </c>
+      <c r="J5" s="10" t="s">
+        <v>375</v>
+      </c>
+      <c r="K5" s="10"/>
+    </row>
+    <row r="6" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="B6" s="10" t="s">
+        <v>380</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>381</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>382</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>383</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>384</v>
+      </c>
+      <c r="G6" s="10" t="s">
+        <v>464</v>
+      </c>
+      <c r="H6" s="10" t="s">
+        <v>465</v>
+      </c>
+      <c r="I6" s="10" t="s">
+        <v>466</v>
+      </c>
+      <c r="J6" s="10" t="s">
+        <v>375</v>
+      </c>
+      <c r="K6" s="10" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="7" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="B7" s="10" t="s">
+        <v>385</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>386</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>387</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>388</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>389</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>467</v>
+      </c>
+      <c r="H7" s="10" t="s">
+        <v>468</v>
+      </c>
+      <c r="I7" s="10" t="s">
+        <v>469</v>
+      </c>
+      <c r="J7" s="10" t="s">
+        <v>390</v>
+      </c>
+      <c r="K7" s="10" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="8" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="B8" s="10" t="s">
+        <v>391</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>392</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="E8" s="10" t="s">
+        <v>394</v>
+      </c>
+      <c r="F8" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="G8" s="10" t="s">
+        <v>470</v>
+      </c>
+      <c r="H8" s="10" t="s">
+        <v>471</v>
+      </c>
+      <c r="I8" s="10" t="s">
+        <v>472</v>
+      </c>
+      <c r="J8" s="10" t="s">
+        <v>375</v>
+      </c>
+      <c r="K8" s="10" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="9" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="B9" s="10"/>
+      <c r="C9" s="10"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="10"/>
+      <c r="F9" s="10"/>
+      <c r="G9" s="10"/>
+      <c r="H9" s="10"/>
+      <c r="I9" s="10"/>
+      <c r="J9" s="10"/>
+      <c r="K9" s="10"/>
+    </row>
+    <row r="10" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="B10" s="10" t="s">
+        <v>395</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>396</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>397</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="F10" s="10" t="s">
+        <v>399</v>
+      </c>
+      <c r="G10" s="10" t="s">
+        <v>473</v>
+      </c>
+      <c r="H10" s="10" t="s">
+        <v>474</v>
+      </c>
+      <c r="I10" s="10" t="s">
+        <v>475</v>
+      </c>
+      <c r="J10" s="10" t="s">
+        <v>400</v>
+      </c>
+      <c r="K10" s="10"/>
+    </row>
+    <row r="11" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="B11" s="10" t="s">
+        <v>401</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>402</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>403</v>
+      </c>
+      <c r="E11" s="10" t="s">
+        <v>404</v>
+      </c>
+      <c r="F11" s="10" t="s">
+        <v>405</v>
+      </c>
+      <c r="G11" s="10" t="s">
+        <v>476</v>
+      </c>
+      <c r="H11" s="10" t="s">
+        <v>477</v>
+      </c>
+      <c r="I11" s="10" t="s">
+        <v>478</v>
+      </c>
+      <c r="J11" s="10" t="s">
+        <v>400</v>
+      </c>
+      <c r="K11" s="10"/>
+    </row>
+    <row r="12" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="B12" s="10" t="s">
+        <v>406</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>407</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>408</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>409</v>
+      </c>
+      <c r="F12" s="10" t="s">
+        <v>410</v>
+      </c>
+      <c r="G12" s="10" t="s">
+        <v>479</v>
+      </c>
+      <c r="H12" s="10" t="s">
+        <v>480</v>
+      </c>
+      <c r="I12" s="10" t="s">
+        <v>481</v>
+      </c>
+      <c r="J12" s="10" t="s">
+        <v>390</v>
+      </c>
+      <c r="K12" s="10"/>
+    </row>
+    <row r="13" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="B13" s="10" t="s">
+        <v>411</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>412</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>413</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>414</v>
+      </c>
+      <c r="F13" s="10" t="s">
+        <v>415</v>
+      </c>
+      <c r="G13" s="10" t="s">
+        <v>482</v>
+      </c>
+      <c r="H13" s="10" t="s">
+        <v>483</v>
+      </c>
+      <c r="I13" s="10" t="s">
+        <v>484</v>
+      </c>
+      <c r="J13" s="10" t="s">
+        <v>390</v>
+      </c>
+      <c r="K13" s="10"/>
+    </row>
+    <row r="14" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="B14" s="10"/>
+      <c r="C14" s="10"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="10"/>
+      <c r="F14" s="10"/>
+      <c r="G14" s="10"/>
+      <c r="H14" s="10"/>
+      <c r="I14" s="10"/>
+      <c r="J14" s="10"/>
+      <c r="K14" s="10"/>
+    </row>
+    <row r="15" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="B15" s="10" t="s">
+        <v>416</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>417</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>418</v>
+      </c>
+      <c r="E15" s="10" t="s">
+        <v>419</v>
+      </c>
+      <c r="F15" s="10" t="s">
+        <v>420</v>
+      </c>
+      <c r="G15" s="10" t="s">
+        <v>485</v>
+      </c>
+      <c r="H15" s="10" t="s">
+        <v>486</v>
+      </c>
+      <c r="I15" s="10" t="s">
+        <v>487</v>
+      </c>
+      <c r="J15" s="10" t="s">
+        <v>400</v>
+      </c>
+      <c r="K15" s="10"/>
+    </row>
+    <row r="16" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="B16" s="10" t="s">
+        <v>421</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="D16" s="10" t="s">
+        <v>423</v>
+      </c>
+      <c r="E16" s="10" t="s">
+        <v>424</v>
+      </c>
+      <c r="F16" s="10" t="s">
+        <v>425</v>
+      </c>
+      <c r="G16" s="10" t="s">
+        <v>488</v>
+      </c>
+      <c r="H16" s="10" t="s">
+        <v>489</v>
+      </c>
+      <c r="I16" s="10" t="s">
+        <v>490</v>
+      </c>
+      <c r="J16" s="10" t="s">
+        <v>400</v>
+      </c>
+      <c r="K16" s="10"/>
+    </row>
+    <row r="17" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="B17" s="10" t="s">
+        <v>426</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>427</v>
+      </c>
+      <c r="D17" s="10" t="s">
+        <v>428</v>
+      </c>
+      <c r="E17" s="10" t="s">
+        <v>409</v>
+      </c>
+      <c r="F17" s="10" t="s">
+        <v>429</v>
+      </c>
+      <c r="G17" s="10" t="s">
+        <v>491</v>
+      </c>
+      <c r="H17" s="10" t="s">
+        <v>492</v>
+      </c>
+      <c r="I17" s="10" t="s">
+        <v>493</v>
+      </c>
+      <c r="J17" s="10" t="s">
+        <v>400</v>
+      </c>
+      <c r="K17" s="10"/>
+    </row>
+    <row r="18" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="B18" s="10" t="s">
+        <v>430</v>
+      </c>
+      <c r="C18" s="10" t="s">
+        <v>431</v>
+      </c>
+      <c r="D18" s="10" t="s">
+        <v>432</v>
+      </c>
+      <c r="E18" s="10" t="s">
+        <v>409</v>
+      </c>
+      <c r="F18" s="10" t="s">
+        <v>433</v>
+      </c>
+      <c r="G18" s="10" t="s">
+        <v>494</v>
+      </c>
+      <c r="H18" s="10" t="s">
+        <v>495</v>
+      </c>
+      <c r="I18" s="10" t="s">
+        <v>463</v>
+      </c>
+      <c r="J18" s="10" t="s">
+        <v>400</v>
+      </c>
+      <c r="K18" s="10"/>
+    </row>
+    <row r="19" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="B19" s="10" t="s">
+        <v>434</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>435</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>436</v>
+      </c>
+      <c r="E19" s="10" t="s">
+        <v>437</v>
+      </c>
+      <c r="F19" s="10" t="s">
+        <v>438</v>
+      </c>
+      <c r="G19" s="10" t="s">
+        <v>496</v>
+      </c>
+      <c r="H19" s="10" t="s">
+        <v>497</v>
+      </c>
+      <c r="I19" s="10" t="s">
+        <v>478</v>
+      </c>
+      <c r="J19" s="10" t="s">
+        <v>400</v>
+      </c>
+      <c r="K19" s="10"/>
+    </row>
+    <row r="20" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="B20" s="10" t="s">
+        <v>439</v>
+      </c>
+      <c r="C20" s="10" t="s">
+        <v>440</v>
+      </c>
+      <c r="D20" s="10" t="s">
+        <v>441</v>
+      </c>
+      <c r="E20" s="10" t="s">
+        <v>409</v>
+      </c>
+      <c r="F20" s="10" t="s">
+        <v>410</v>
+      </c>
+      <c r="G20" s="10" t="s">
+        <v>498</v>
+      </c>
+      <c r="H20" s="10" t="s">
+        <v>480</v>
+      </c>
+      <c r="I20" s="10" t="s">
+        <v>463</v>
+      </c>
+      <c r="J20" s="10" t="s">
+        <v>390</v>
+      </c>
+      <c r="K20" s="10"/>
+    </row>
+    <row r="21" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="B21" s="10" t="s">
+        <v>442</v>
+      </c>
+      <c r="C21" s="10" t="s">
+        <v>443</v>
+      </c>
+      <c r="D21" s="10" t="s">
+        <v>444</v>
+      </c>
+      <c r="E21" s="10" t="s">
+        <v>445</v>
+      </c>
+      <c r="F21" s="10" t="s">
+        <v>446</v>
+      </c>
+      <c r="G21" s="10" t="s">
+        <v>499</v>
+      </c>
+      <c r="H21" s="10" t="s">
+        <v>483</v>
+      </c>
+      <c r="I21" s="10" t="s">
+        <v>500</v>
+      </c>
+      <c r="J21" s="10" t="s">
+        <v>390</v>
+      </c>
+      <c r="K21" s="10"/>
+    </row>
+    <row r="22" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="B22" s="10"/>
+      <c r="C22" s="10"/>
+      <c r="D22" s="10"/>
+      <c r="E22" s="10"/>
+      <c r="F22" s="10"/>
+      <c r="G22" s="10"/>
+      <c r="H22" s="10"/>
+      <c r="I22" s="10"/>
+      <c r="J22" s="10"/>
+      <c r="K22" s="10"/>
+    </row>
+    <row r="23" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="B23" s="10" t="s">
+        <v>447</v>
+      </c>
+      <c r="C23" s="10" t="s">
+        <v>448</v>
+      </c>
+      <c r="D23" s="10" t="s">
+        <v>449</v>
+      </c>
+      <c r="E23" s="10" t="s">
+        <v>409</v>
+      </c>
+      <c r="F23" s="10" t="s">
+        <v>450</v>
+      </c>
+      <c r="G23" s="10" t="s">
+        <v>501</v>
+      </c>
+      <c r="H23" s="10" t="s">
+        <v>502</v>
+      </c>
+      <c r="I23" s="10" t="s">
+        <v>503</v>
+      </c>
+      <c r="J23" s="10" t="s">
+        <v>400</v>
+      </c>
+      <c r="K23" s="10"/>
+    </row>
+    <row r="24" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="B24" s="10" t="s">
+        <v>451</v>
+      </c>
+      <c r="C24" s="10" t="s">
+        <v>452</v>
+      </c>
+      <c r="D24" s="10" t="s">
+        <v>453</v>
+      </c>
+      <c r="E24" s="10" t="s">
+        <v>454</v>
+      </c>
+      <c r="F24" s="10" t="s">
+        <v>410</v>
+      </c>
+      <c r="G24" s="10" t="s">
+        <v>504</v>
+      </c>
+      <c r="H24" s="10" t="s">
+        <v>480</v>
+      </c>
+      <c r="I24" s="10" t="s">
+        <v>505</v>
+      </c>
+      <c r="J24" s="10" t="s">
+        <v>390</v>
+      </c>
+      <c r="K24" s="10"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:K2"/>
+  </mergeCells>
+  <phoneticPr fontId="2"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6440C622-5C63-4B02-9823-634F172241E7}">
   <dimension ref="B2:AI132"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>

--- a/docs/01_overview/要件定義.xlsx
+++ b/docs/01_overview/要件定義.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36DAA855-F265-40C7-92DD-D0E294E6A746}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{2761BF75-AFA8-428B-9FA1-0F0E7899F9CA}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{2761BF75-AFA8-428B-9FA1-0F0E7899F9CA}"/>
   </bookViews>
   <sheets>
     <sheet name="要件定義" sheetId="3" r:id="rId1"/>

--- a/docs/01_overview/要件定義.xlsx
+++ b/docs/01_overview/要件定義.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ktakw\sg-mock-test-system\docs\01_overview\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36DAA855-F265-40C7-92DD-D0E294E6A746}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C05D2334-CDD2-4E36-B45B-0BDA92E8B6FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{2761BF75-AFA8-428B-9FA1-0F0E7899F9CA}"/>
   </bookViews>
   <sheets>
     <sheet name="要件定義" sheetId="3" r:id="rId1"/>
-    <sheet name="機能一覧" sheetId="4" r:id="rId2"/>
+    <sheet name="機能一覧" sheetId="5" r:id="rId2"/>
     <sheet name="要件定義メモ" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="595" uniqueCount="512">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="599" uniqueCount="515">
   <si>
     <t>1 システム概要</t>
   </si>
@@ -1284,9 +1284,6 @@
     <t>※詳細は機能一覧（A-01〜HIS-02）に準拠する。</t>
   </si>
   <si>
-    <t>■ アカウント機能</t>
-  </si>
-  <si>
     <t>新規登録／更新／削除</t>
   </si>
   <si>
@@ -1922,9 +1919,6 @@
     <t>受験時間外不可、再受験制御あり</t>
   </si>
   <si>
-    <t>状態管理必要</t>
-  </si>
-  <si>
     <t>開始時刻記録→終了時刻算出→タイマー更新→自動終了</t>
   </si>
   <si>
@@ -1977,35 +1971,51 @@
   </si>
   <si>
     <t>フィルタ可能</t>
-  </si>
-  <si>
-    <t>機能一覧</t>
-    <rPh sb="0" eb="4">
-      <t>キノウイチラン</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>C</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>R</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>U</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>D</t>
-    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>CRUD要素</t>
     <rPh sb="4" eb="6">
       <t>ヨウソ</t>
     </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>機能一覧  ─  SG 模擬試験システム</t>
+    <rPh sb="0" eb="2">
+      <t>キノウ</t>
+    </rPh>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>■ アカウント機能</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>R</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>U</t>
+  </si>
+  <si>
+    <t>■ 受験前機能（Preparation）</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>■ 受験機能（Execute）</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>状態管理必要</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>■ 受験後機能（History）</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -2013,7 +2023,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2064,8 +2074,122 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color theme="0"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF2C2C2A"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF2C2C2A"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF3C3489"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF2C2C2A"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF5F5E5A"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF085041"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF633806"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2074,18 +2198,74 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
+        <fgColor rgb="FF2C2C2A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF444441"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
+        <fgColor rgb="FF534AB7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAFAF8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEEDFE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0EFEB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEEDFE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D9E75"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE1F5EE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0EFEB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBA7517"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAEEDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF185FA5"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -2108,13 +2288,152 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF2C2C2A"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF444441"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF444441"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF444441"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF444441"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF534AB7"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD3D1C7"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD3D1C7"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD3D1C7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD3D1C7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF534AB7"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF534AB7"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF534AB7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF534AB7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF1D9E75"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF1D9E75"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF1D9E75"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF1D9E75"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF1D9E75"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBA7517"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBA7517"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBA7517"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBA7517"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBA7517"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF185FA5"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF185FA5"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF185FA5"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF185FA5"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF185FA5"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2145,18 +2464,155 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" xfId="2" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" xfId="2" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="3">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="標準 2" xfId="1" xr:uid="{F3A57F7F-0378-481B-B117-A795575D852C}"/>
+    <cellStyle name="標準 2 2" xfId="2" xr:uid="{B5DD0EB9-D7D4-4556-BD01-3AFAA0169A19}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -3445,17 +3901,17 @@
     </row>
     <row r="13" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B13" s="7" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="14" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B14" s="7" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="15" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B15" s="7" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="17" spans="2:2" x14ac:dyDescent="0.45">
@@ -3475,7 +3931,7 @@
     </row>
     <row r="25" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B25" s="7" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="26" spans="2:2" x14ac:dyDescent="0.45">
@@ -3525,12 +3981,12 @@
     </row>
     <row r="43" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B43" s="7" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="44" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B44" s="7" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="46" spans="2:2" ht="22.2" x14ac:dyDescent="0.45">
@@ -3600,7 +4056,7 @@
     </row>
     <row r="67" spans="2:2" ht="22.2" x14ac:dyDescent="0.45">
       <c r="B67" s="9" t="s">
-        <v>282</v>
+        <v>506</v>
       </c>
     </row>
     <row r="69" spans="2:2" x14ac:dyDescent="0.45">
@@ -3610,32 +4066,32 @@
     </row>
     <row r="70" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B70" s="7" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="72" spans="2:2" ht="22.2" x14ac:dyDescent="0.45">
       <c r="B72" s="9" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="74" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B74" s="7" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="75" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B75" s="7" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="76" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B76" s="7" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="78" spans="2:2" ht="22.2" x14ac:dyDescent="0.45">
       <c r="B78" s="9" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="80" spans="2:2" x14ac:dyDescent="0.45">
@@ -3645,347 +4101,347 @@
     </row>
     <row r="81" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B81" s="7" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="82" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B82" s="7" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="83" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B83" s="7" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="84" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B84" s="7" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="86" spans="2:2" ht="22.2" x14ac:dyDescent="0.45">
       <c r="B86" s="9" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="88" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B88" s="7" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="89" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B89" s="7" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="93" spans="2:2" ht="28.8" x14ac:dyDescent="0.45">
       <c r="B93" s="8" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="95" spans="2:2" ht="22.2" x14ac:dyDescent="0.45">
       <c r="B95" s="9" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="97" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B97" s="7" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="98" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B98" s="7" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="100" spans="2:2" ht="22.2" x14ac:dyDescent="0.45">
       <c r="B100" s="9" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="102" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B102" s="7" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="103" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B103" s="7" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="105" spans="2:2" ht="22.2" x14ac:dyDescent="0.45">
       <c r="B105" s="9" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="107" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B107" s="7" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="108" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B108" s="7" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="109" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B109" s="7" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="111" spans="2:2" ht="22.2" x14ac:dyDescent="0.45">
       <c r="B111" s="9" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="113" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B113" s="7" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="114" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B114" s="7" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="118" spans="2:2" ht="28.8" x14ac:dyDescent="0.45">
       <c r="B118" s="8" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="120" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B120" s="7" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="122" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B122" s="7" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="123" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B123" s="7" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="124" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B124" s="7" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="125" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B125" s="7" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="126" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B126" s="7" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="127" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B127" s="7" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="128" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B128" s="7" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="129" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B129" s="7" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="133" spans="2:2" ht="28.8" x14ac:dyDescent="0.45">
       <c r="B133" s="8" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="135" spans="2:2" ht="22.2" x14ac:dyDescent="0.45">
       <c r="B135" s="9" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="137" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B137" s="7" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="138" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B138" s="7" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="139" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B139" s="7" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="140" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B140" s="7" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="141" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B141" s="7" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="145" spans="2:2" ht="28.8" x14ac:dyDescent="0.45">
       <c r="B145" s="8" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="147" spans="2:2" ht="22.2" x14ac:dyDescent="0.45">
       <c r="B147" s="9" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="149" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B149" s="7" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="151" spans="2:2" ht="22.2" x14ac:dyDescent="0.45">
       <c r="B151" s="9" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="153" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B153" s="7" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="155" spans="2:2" ht="22.2" x14ac:dyDescent="0.45">
       <c r="B155" s="9" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="157" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B157" s="7" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="161" spans="2:2" ht="28.8" x14ac:dyDescent="0.45">
       <c r="B161" s="8" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="163" spans="2:2" ht="22.2" x14ac:dyDescent="0.45">
       <c r="B163" s="9" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="165" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B165" s="7" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="167" spans="2:2" ht="22.2" x14ac:dyDescent="0.45">
       <c r="B167" s="9" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="169" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B169" s="7" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="170" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B170" s="7" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="174" spans="2:2" ht="28.8" x14ac:dyDescent="0.45">
       <c r="B174" s="8" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="176" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B176" s="7" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="177" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B177" s="7" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="178" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B178" s="7" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="182" spans="2:2" ht="28.8" x14ac:dyDescent="0.45">
       <c r="B182" s="8" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="184" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B184" s="7" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="186" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B186" s="7" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="187" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B187" s="7" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="191" spans="2:2" ht="28.8" x14ac:dyDescent="0.45">
       <c r="B191" s="8" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="193" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B193" s="7" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="194" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B194" s="7" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="195" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B195" s="7" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="199" spans="2:2" ht="28.8" x14ac:dyDescent="0.45">
       <c r="B199" s="8" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="201" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B201" s="7" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="202" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B202" s="7" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="203" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B203" s="7" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="207" spans="2:2" ht="28.8" x14ac:dyDescent="0.45">
       <c r="B207" s="8" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="209" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B209" s="7" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
   </sheetData>
@@ -3995,656 +4451,701 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A0697D5-EC04-49BC-B882-B72733D97B34}">
-  <dimension ref="B2:K24"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{551EDAA6-A4EC-4ADE-BF4E-C072C82ECD1C}">
+  <dimension ref="B2:M25"/>
+  <sheetFormatPr defaultRowHeight="18" outlineLevelCol="1" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.3984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="27.59765625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="33.69921875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="63" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="42.09765625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="27.59765625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.09765625" style="10" customWidth="1"/>
+    <col min="2" max="2" width="9.09765625" style="10" customWidth="1"/>
+    <col min="3" max="3" width="6.8984375" style="10" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.296875" style="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.69921875" style="10" customWidth="1"/>
+    <col min="6" max="6" width="27.69921875" style="10" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="7" max="7" width="31.5" style="10" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="8" max="8" width="25.09765625" style="10" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="9" max="9" width="39.796875" style="10" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="10" max="10" width="26.09765625" style="10" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="11" max="11" width="10.3984375" style="10" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="12" max="12" width="8.8984375" style="10" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="13" max="13" width="8.796875" style="10" collapsed="1"/>
+    <col min="14" max="16384" width="8.796875" style="10"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:11" x14ac:dyDescent="0.45">
-      <c r="B2" s="12" t="s">
+    <row r="2" spans="2:12" ht="22.2" x14ac:dyDescent="0.45">
+      <c r="B2" s="58" t="s">
+        <v>505</v>
+      </c>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
+      <c r="I2" s="59"/>
+      <c r="J2" s="59"/>
+      <c r="K2" s="59"/>
+      <c r="L2" s="59"/>
+    </row>
+    <row r="3" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B3" s="11"/>
+      <c r="C3" s="11" t="s">
+        <v>363</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>364</v>
+      </c>
+      <c r="E3" s="12" t="s">
+        <v>365</v>
+      </c>
+      <c r="F3" s="12" t="s">
+        <v>366</v>
+      </c>
+      <c r="G3" s="12" t="s">
+        <v>367</v>
+      </c>
+      <c r="H3" s="12" t="s">
+        <v>454</v>
+      </c>
+      <c r="I3" s="12" t="s">
+        <v>455</v>
+      </c>
+      <c r="J3" s="12" t="s">
+        <v>456</v>
+      </c>
+      <c r="K3" s="12" t="s">
+        <v>368</v>
+      </c>
+      <c r="L3" s="12" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B4" s="13" t="s">
         <v>506</v>
       </c>
-      <c r="C2" s="12"/>
-      <c r="D2" s="12"/>
-      <c r="E2" s="12"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="12"/>
-      <c r="H2" s="12"/>
-      <c r="I2" s="12"/>
-      <c r="J2" s="12"/>
-      <c r="K2" s="12"/>
-    </row>
-    <row r="3" spans="2:11" x14ac:dyDescent="0.45">
-      <c r="B3" s="11" t="s">
-        <v>364</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>365</v>
-      </c>
-      <c r="D3" s="11" t="s">
-        <v>366</v>
-      </c>
-      <c r="E3" s="11" t="s">
-        <v>367</v>
-      </c>
-      <c r="F3" s="11" t="s">
-        <v>368</v>
-      </c>
-      <c r="G3" s="11" t="s">
-        <v>455</v>
-      </c>
-      <c r="H3" s="11" t="s">
-        <v>456</v>
-      </c>
-      <c r="I3" s="11" t="s">
+      <c r="C4" s="14"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="14"/>
+      <c r="G4" s="14"/>
+      <c r="H4" s="14"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="14"/>
+      <c r="K4" s="14"/>
+      <c r="L4" s="14"/>
+    </row>
+    <row r="5" spans="2:12" ht="30" x14ac:dyDescent="0.45">
+      <c r="B5" s="15"/>
+      <c r="C5" s="16" t="s">
+        <v>369</v>
+      </c>
+      <c r="D5" s="17" t="s">
+        <v>370</v>
+      </c>
+      <c r="E5" s="18" t="s">
+        <v>371</v>
+      </c>
+      <c r="F5" s="19" t="s">
+        <v>372</v>
+      </c>
+      <c r="G5" s="20" t="s">
+        <v>373</v>
+      </c>
+      <c r="H5" s="21" t="s">
         <v>457</v>
       </c>
-      <c r="J3" s="11" t="s">
-        <v>369</v>
-      </c>
-      <c r="K3" s="11" t="s">
+      <c r="I5" s="22" t="s">
+        <v>458</v>
+      </c>
+      <c r="J5" s="22" t="s">
+        <v>459</v>
+      </c>
+      <c r="K5" s="22" t="s">
+        <v>374</v>
+      </c>
+      <c r="L5" s="23" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B6" s="24"/>
+      <c r="C6" s="16" t="s">
+        <v>375</v>
+      </c>
+      <c r="D6" s="25" t="s">
+        <v>376</v>
+      </c>
+      <c r="E6" s="26" t="s">
+        <v>377</v>
+      </c>
+      <c r="F6" s="27" t="s">
+        <v>378</v>
+      </c>
+      <c r="G6" s="28" t="s">
+        <v>311</v>
+      </c>
+      <c r="H6" s="29" t="s">
+        <v>460</v>
+      </c>
+      <c r="I6" s="30" t="s">
+        <v>461</v>
+      </c>
+      <c r="J6" s="30" t="s">
+        <v>462</v>
+      </c>
+      <c r="K6" s="30" t="s">
+        <v>374</v>
+      </c>
+      <c r="L6" s="31"/>
+    </row>
+    <row r="7" spans="2:12" ht="30" x14ac:dyDescent="0.45">
+      <c r="B7" s="15"/>
+      <c r="C7" s="16" t="s">
+        <v>379</v>
+      </c>
+      <c r="D7" s="17" t="s">
+        <v>380</v>
+      </c>
+      <c r="E7" s="26" t="s">
+        <v>381</v>
+      </c>
+      <c r="F7" s="19" t="s">
+        <v>382</v>
+      </c>
+      <c r="G7" s="20" t="s">
+        <v>383</v>
+      </c>
+      <c r="H7" s="21" t="s">
+        <v>463</v>
+      </c>
+      <c r="I7" s="22" t="s">
+        <v>464</v>
+      </c>
+      <c r="J7" s="22" t="s">
+        <v>465</v>
+      </c>
+      <c r="K7" s="22" t="s">
+        <v>374</v>
+      </c>
+      <c r="L7" s="23" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" ht="30" x14ac:dyDescent="0.45">
+      <c r="B8" s="24"/>
+      <c r="C8" s="16" t="s">
+        <v>384</v>
+      </c>
+      <c r="D8" s="25" t="s">
+        <v>385</v>
+      </c>
+      <c r="E8" s="26" t="s">
+        <v>386</v>
+      </c>
+      <c r="F8" s="27" t="s">
+        <v>387</v>
+      </c>
+      <c r="G8" s="28" t="s">
+        <v>388</v>
+      </c>
+      <c r="H8" s="29" t="s">
+        <v>466</v>
+      </c>
+      <c r="I8" s="30" t="s">
+        <v>467</v>
+      </c>
+      <c r="J8" s="30" t="s">
+        <v>468</v>
+      </c>
+      <c r="K8" s="30" t="s">
+        <v>389</v>
+      </c>
+      <c r="L8" s="31" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="9" spans="2:12" ht="60" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B9" s="32"/>
+      <c r="C9" s="16" t="s">
+        <v>390</v>
+      </c>
+      <c r="D9" s="33" t="s">
+        <v>391</v>
+      </c>
+      <c r="E9" s="18" t="s">
+        <v>392</v>
+      </c>
+      <c r="F9" s="34" t="s">
+        <v>393</v>
+      </c>
+      <c r="G9" s="35" t="s">
+        <v>66</v>
+      </c>
+      <c r="H9" s="36" t="s">
+        <v>469</v>
+      </c>
+      <c r="I9" s="22" t="s">
+        <v>470</v>
+      </c>
+      <c r="J9" s="22" t="s">
+        <v>471</v>
+      </c>
+      <c r="K9" s="22" t="s">
+        <v>374</v>
+      </c>
+      <c r="L9" s="23" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B10" s="37" t="s">
         <v>511</v>
       </c>
-    </row>
-    <row r="4" spans="2:11" x14ac:dyDescent="0.45">
-      <c r="B4" s="10" t="s">
-        <v>370</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>371</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>372</v>
-      </c>
-      <c r="E4" s="10" t="s">
-        <v>373</v>
-      </c>
-      <c r="F4" s="10" t="s">
-        <v>374</v>
-      </c>
-      <c r="G4" s="10" t="s">
-        <v>458</v>
-      </c>
-      <c r="H4" s="10" t="s">
-        <v>459</v>
-      </c>
-      <c r="I4" s="10" t="s">
-        <v>460</v>
-      </c>
-      <c r="J4" s="10" t="s">
-        <v>375</v>
-      </c>
-      <c r="K4" s="10" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.45">
-      <c r="B5" s="10" t="s">
-        <v>376</v>
-      </c>
-      <c r="C5" s="10" t="s">
-        <v>377</v>
-      </c>
-      <c r="D5" s="10" t="s">
-        <v>378</v>
-      </c>
-      <c r="E5" s="10" t="s">
-        <v>379</v>
-      </c>
-      <c r="F5" s="10" t="s">
-        <v>312</v>
-      </c>
-      <c r="G5" s="10" t="s">
-        <v>461</v>
-      </c>
-      <c r="H5" s="10" t="s">
+      <c r="C10" s="38"/>
+      <c r="D10" s="38"/>
+      <c r="E10" s="38"/>
+      <c r="F10" s="38"/>
+      <c r="G10" s="38"/>
+      <c r="H10" s="38"/>
+      <c r="I10" s="38"/>
+      <c r="J10" s="38"/>
+      <c r="K10" s="38"/>
+      <c r="L10" s="38"/>
+    </row>
+    <row r="11" spans="2:12" ht="30" x14ac:dyDescent="0.45">
+      <c r="B11" s="15"/>
+      <c r="C11" s="39" t="s">
+        <v>394</v>
+      </c>
+      <c r="D11" s="17" t="s">
+        <v>395</v>
+      </c>
+      <c r="E11" s="40" t="s">
+        <v>396</v>
+      </c>
+      <c r="F11" s="19" t="s">
+        <v>397</v>
+      </c>
+      <c r="G11" s="20" t="s">
+        <v>398</v>
+      </c>
+      <c r="H11" s="21" t="s">
+        <v>472</v>
+      </c>
+      <c r="I11" s="22" t="s">
+        <v>473</v>
+      </c>
+      <c r="J11" s="22" t="s">
+        <v>474</v>
+      </c>
+      <c r="K11" s="22" t="s">
+        <v>399</v>
+      </c>
+      <c r="L11" s="22"/>
+    </row>
+    <row r="12" spans="2:12" ht="45" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B12" s="41"/>
+      <c r="C12" s="39" t="s">
+        <v>400</v>
+      </c>
+      <c r="D12" s="42" t="s">
+        <v>401</v>
+      </c>
+      <c r="E12" s="40" t="s">
+        <v>402</v>
+      </c>
+      <c r="F12" s="27" t="s">
+        <v>403</v>
+      </c>
+      <c r="G12" s="28" t="s">
+        <v>404</v>
+      </c>
+      <c r="H12" s="29" t="s">
+        <v>475</v>
+      </c>
+      <c r="I12" s="30" t="s">
+        <v>476</v>
+      </c>
+      <c r="J12" s="30" t="s">
+        <v>477</v>
+      </c>
+      <c r="K12" s="30" t="s">
+        <v>399</v>
+      </c>
+      <c r="L12" s="30"/>
+    </row>
+    <row r="13" spans="2:12" ht="60" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B13" s="15"/>
+      <c r="C13" s="39" t="s">
+        <v>405</v>
+      </c>
+      <c r="D13" s="17" t="s">
+        <v>406</v>
+      </c>
+      <c r="E13" s="40" t="s">
+        <v>407</v>
+      </c>
+      <c r="F13" s="19" t="s">
+        <v>408</v>
+      </c>
+      <c r="G13" s="20" t="s">
+        <v>409</v>
+      </c>
+      <c r="H13" s="21" t="s">
+        <v>478</v>
+      </c>
+      <c r="I13" s="22" t="s">
+        <v>479</v>
+      </c>
+      <c r="J13" s="22" t="s">
+        <v>480</v>
+      </c>
+      <c r="K13" s="22" t="s">
+        <v>389</v>
+      </c>
+      <c r="L13" s="22"/>
+    </row>
+    <row r="14" spans="2:12" ht="30" x14ac:dyDescent="0.45">
+      <c r="B14" s="41"/>
+      <c r="C14" s="39" t="s">
+        <v>410</v>
+      </c>
+      <c r="D14" s="42" t="s">
+        <v>411</v>
+      </c>
+      <c r="E14" s="40" t="s">
+        <v>412</v>
+      </c>
+      <c r="F14" s="43" t="s">
+        <v>413</v>
+      </c>
+      <c r="G14" s="44" t="s">
+        <v>414</v>
+      </c>
+      <c r="H14" s="45" t="s">
+        <v>481</v>
+      </c>
+      <c r="I14" s="30" t="s">
+        <v>482</v>
+      </c>
+      <c r="J14" s="30" t="s">
+        <v>483</v>
+      </c>
+      <c r="K14" s="30" t="s">
+        <v>389</v>
+      </c>
+      <c r="L14" s="30"/>
+    </row>
+    <row r="15" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B15" s="46" t="s">
+        <v>512</v>
+      </c>
+      <c r="C15" s="47"/>
+      <c r="D15" s="47"/>
+      <c r="E15" s="47"/>
+      <c r="F15" s="47"/>
+      <c r="G15" s="47"/>
+      <c r="H15" s="47"/>
+      <c r="I15" s="47"/>
+      <c r="J15" s="47"/>
+      <c r="K15" s="47"/>
+      <c r="L15" s="47"/>
+    </row>
+    <row r="16" spans="2:12" ht="30" x14ac:dyDescent="0.45">
+      <c r="B16" s="15"/>
+      <c r="C16" s="48" t="s">
+        <v>415</v>
+      </c>
+      <c r="D16" s="17" t="s">
+        <v>416</v>
+      </c>
+      <c r="E16" s="49" t="s">
+        <v>417</v>
+      </c>
+      <c r="F16" s="19" t="s">
+        <v>418</v>
+      </c>
+      <c r="G16" s="20" t="s">
+        <v>419</v>
+      </c>
+      <c r="H16" s="21" t="s">
+        <v>484</v>
+      </c>
+      <c r="I16" s="22" t="s">
+        <v>485</v>
+      </c>
+      <c r="J16" s="22" t="s">
+        <v>513</v>
+      </c>
+      <c r="K16" s="22" t="s">
+        <v>399</v>
+      </c>
+      <c r="L16" s="22"/>
+    </row>
+    <row r="17" spans="2:12" ht="30" x14ac:dyDescent="0.45">
+      <c r="B17" s="41"/>
+      <c r="C17" s="48" t="s">
+        <v>420</v>
+      </c>
+      <c r="D17" s="42" t="s">
+        <v>421</v>
+      </c>
+      <c r="E17" s="49" t="s">
+        <v>422</v>
+      </c>
+      <c r="F17" s="43" t="s">
+        <v>423</v>
+      </c>
+      <c r="G17" s="44" t="s">
+        <v>424</v>
+      </c>
+      <c r="H17" s="45" t="s">
+        <v>486</v>
+      </c>
+      <c r="I17" s="30" t="s">
+        <v>487</v>
+      </c>
+      <c r="J17" s="30" t="s">
+        <v>488</v>
+      </c>
+      <c r="K17" s="30" t="s">
+        <v>399</v>
+      </c>
+      <c r="L17" s="30"/>
+    </row>
+    <row r="18" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B18" s="15"/>
+      <c r="C18" s="48" t="s">
+        <v>425</v>
+      </c>
+      <c r="D18" s="17" t="s">
+        <v>426</v>
+      </c>
+      <c r="E18" s="49" t="s">
+        <v>427</v>
+      </c>
+      <c r="F18" s="19" t="s">
+        <v>408</v>
+      </c>
+      <c r="G18" s="20" t="s">
+        <v>428</v>
+      </c>
+      <c r="H18" s="21" t="s">
+        <v>489</v>
+      </c>
+      <c r="I18" s="22" t="s">
+        <v>490</v>
+      </c>
+      <c r="J18" s="22" t="s">
+        <v>491</v>
+      </c>
+      <c r="K18" s="22" t="s">
+        <v>399</v>
+      </c>
+      <c r="L18" s="22"/>
+    </row>
+    <row r="19" spans="2:12" ht="30" x14ac:dyDescent="0.45">
+      <c r="B19" s="41"/>
+      <c r="C19" s="48" t="s">
+        <v>429</v>
+      </c>
+      <c r="D19" s="42" t="s">
+        <v>430</v>
+      </c>
+      <c r="E19" s="49" t="s">
+        <v>431</v>
+      </c>
+      <c r="F19" s="43" t="s">
+        <v>408</v>
+      </c>
+      <c r="G19" s="44" t="s">
+        <v>432</v>
+      </c>
+      <c r="H19" s="45" t="s">
+        <v>492</v>
+      </c>
+      <c r="I19" s="30" t="s">
+        <v>493</v>
+      </c>
+      <c r="J19" s="30" t="s">
         <v>462</v>
       </c>
-      <c r="I5" s="10" t="s">
-        <v>463</v>
-      </c>
-      <c r="J5" s="10" t="s">
-        <v>375</v>
-      </c>
-      <c r="K5" s="10"/>
-    </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.45">
-      <c r="B6" s="10" t="s">
-        <v>380</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>381</v>
-      </c>
-      <c r="D6" s="10" t="s">
-        <v>382</v>
-      </c>
-      <c r="E6" s="10" t="s">
-        <v>383</v>
-      </c>
-      <c r="F6" s="10" t="s">
-        <v>384</v>
-      </c>
-      <c r="G6" s="10" t="s">
-        <v>464</v>
-      </c>
-      <c r="H6" s="10" t="s">
-        <v>465</v>
-      </c>
-      <c r="I6" s="10" t="s">
-        <v>466</v>
-      </c>
-      <c r="J6" s="10" t="s">
-        <v>375</v>
-      </c>
-      <c r="K6" s="10" t="s">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.45">
-      <c r="B7" s="10" t="s">
-        <v>385</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>386</v>
-      </c>
-      <c r="D7" s="10" t="s">
-        <v>387</v>
-      </c>
-      <c r="E7" s="10" t="s">
-        <v>388</v>
-      </c>
-      <c r="F7" s="10" t="s">
+      <c r="K19" s="30" t="s">
+        <v>399</v>
+      </c>
+      <c r="L19" s="30"/>
+    </row>
+    <row r="20" spans="2:12" ht="30" x14ac:dyDescent="0.45">
+      <c r="B20" s="15"/>
+      <c r="C20" s="48" t="s">
+        <v>433</v>
+      </c>
+      <c r="D20" s="17" t="s">
+        <v>434</v>
+      </c>
+      <c r="E20" s="49" t="s">
+        <v>435</v>
+      </c>
+      <c r="F20" s="19" t="s">
+        <v>436</v>
+      </c>
+      <c r="G20" s="20" t="s">
+        <v>437</v>
+      </c>
+      <c r="H20" s="21" t="s">
+        <v>494</v>
+      </c>
+      <c r="I20" s="22" t="s">
+        <v>495</v>
+      </c>
+      <c r="J20" s="22" t="s">
+        <v>477</v>
+      </c>
+      <c r="K20" s="22" t="s">
+        <v>399</v>
+      </c>
+      <c r="L20" s="22"/>
+    </row>
+    <row r="21" spans="2:12" ht="32.4" x14ac:dyDescent="0.45">
+      <c r="B21" s="41"/>
+      <c r="C21" s="48" t="s">
+        <v>438</v>
+      </c>
+      <c r="D21" s="42" t="s">
+        <v>439</v>
+      </c>
+      <c r="E21" s="49" t="s">
+        <v>440</v>
+      </c>
+      <c r="F21" s="43" t="s">
+        <v>408</v>
+      </c>
+      <c r="G21" s="44" t="s">
+        <v>409</v>
+      </c>
+      <c r="H21" s="45" t="s">
+        <v>496</v>
+      </c>
+      <c r="I21" s="30" t="s">
+        <v>479</v>
+      </c>
+      <c r="J21" s="30" t="s">
+        <v>462</v>
+      </c>
+      <c r="K21" s="30" t="s">
         <v>389</v>
       </c>
-      <c r="G7" s="10" t="s">
-        <v>467</v>
-      </c>
-      <c r="H7" s="10" t="s">
-        <v>468</v>
-      </c>
-      <c r="I7" s="10" t="s">
-        <v>469</v>
-      </c>
-      <c r="J7" s="10" t="s">
-        <v>390</v>
-      </c>
-      <c r="K7" s="10" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.45">
-      <c r="B8" s="10" t="s">
-        <v>391</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>392</v>
-      </c>
-      <c r="D8" s="10" t="s">
-        <v>393</v>
-      </c>
-      <c r="E8" s="10" t="s">
-        <v>394</v>
-      </c>
-      <c r="F8" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="G8" s="10" t="s">
-        <v>470</v>
-      </c>
-      <c r="H8" s="10" t="s">
-        <v>471</v>
-      </c>
-      <c r="I8" s="10" t="s">
-        <v>472</v>
-      </c>
-      <c r="J8" s="10" t="s">
-        <v>375</v>
-      </c>
-      <c r="K8" s="10" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.45">
-      <c r="B9" s="10"/>
-      <c r="C9" s="10"/>
-      <c r="D9" s="10"/>
-      <c r="E9" s="10"/>
-      <c r="F9" s="10"/>
-      <c r="G9" s="10"/>
-      <c r="H9" s="10"/>
-      <c r="I9" s="10"/>
-      <c r="J9" s="10"/>
-      <c r="K9" s="10"/>
-    </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.45">
-      <c r="B10" s="10" t="s">
-        <v>395</v>
-      </c>
-      <c r="C10" s="10" t="s">
-        <v>396</v>
-      </c>
-      <c r="D10" s="10" t="s">
-        <v>397</v>
-      </c>
-      <c r="E10" s="10" t="s">
-        <v>398</v>
-      </c>
-      <c r="F10" s="10" t="s">
+      <c r="L21" s="30"/>
+    </row>
+    <row r="22" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B22" s="15"/>
+      <c r="C22" s="48" t="s">
+        <v>441</v>
+      </c>
+      <c r="D22" s="17" t="s">
+        <v>442</v>
+      </c>
+      <c r="E22" s="49" t="s">
+        <v>443</v>
+      </c>
+      <c r="F22" s="19" t="s">
+        <v>444</v>
+      </c>
+      <c r="G22" s="20" t="s">
+        <v>445</v>
+      </c>
+      <c r="H22" s="21" t="s">
+        <v>497</v>
+      </c>
+      <c r="I22" s="22" t="s">
+        <v>482</v>
+      </c>
+      <c r="J22" s="22" t="s">
+        <v>498</v>
+      </c>
+      <c r="K22" s="22" t="s">
+        <v>389</v>
+      </c>
+      <c r="L22" s="22"/>
+    </row>
+    <row r="23" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B23" s="50" t="s">
+        <v>514</v>
+      </c>
+      <c r="C23" s="51"/>
+      <c r="D23" s="51"/>
+      <c r="E23" s="51"/>
+      <c r="F23" s="51"/>
+      <c r="G23" s="51"/>
+      <c r="H23" s="51"/>
+      <c r="I23" s="51"/>
+      <c r="J23" s="51"/>
+      <c r="K23" s="51"/>
+      <c r="L23" s="51"/>
+    </row>
+    <row r="24" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B24" s="52"/>
+      <c r="C24" s="53" t="s">
+        <v>446</v>
+      </c>
+      <c r="D24" s="54" t="s">
+        <v>447</v>
+      </c>
+      <c r="E24" s="55" t="s">
+        <v>448</v>
+      </c>
+      <c r="F24" s="21" t="s">
+        <v>408</v>
+      </c>
+      <c r="G24" s="20" t="s">
+        <v>449</v>
+      </c>
+      <c r="H24" s="21" t="s">
+        <v>499</v>
+      </c>
+      <c r="I24" s="22" t="s">
+        <v>500</v>
+      </c>
+      <c r="J24" s="22" t="s">
+        <v>501</v>
+      </c>
+      <c r="K24" s="22" t="s">
         <v>399</v>
       </c>
-      <c r="G10" s="10" t="s">
-        <v>473</v>
-      </c>
-      <c r="H10" s="10" t="s">
-        <v>474</v>
-      </c>
-      <c r="I10" s="10" t="s">
-        <v>475</v>
-      </c>
-      <c r="J10" s="10" t="s">
-        <v>400</v>
-      </c>
-      <c r="K10" s="10"/>
-    </row>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.45">
-      <c r="B11" s="10" t="s">
-        <v>401</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>402</v>
-      </c>
-      <c r="D11" s="10" t="s">
-        <v>403</v>
-      </c>
-      <c r="E11" s="10" t="s">
-        <v>404</v>
-      </c>
-      <c r="F11" s="10" t="s">
-        <v>405</v>
-      </c>
-      <c r="G11" s="10" t="s">
-        <v>476</v>
-      </c>
-      <c r="H11" s="10" t="s">
-        <v>477</v>
-      </c>
-      <c r="I11" s="10" t="s">
-        <v>478</v>
-      </c>
-      <c r="J11" s="10" t="s">
-        <v>400</v>
-      </c>
-      <c r="K11" s="10"/>
-    </row>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.45">
-      <c r="B12" s="10" t="s">
-        <v>406</v>
-      </c>
-      <c r="C12" s="10" t="s">
-        <v>407</v>
-      </c>
-      <c r="D12" s="10" t="s">
-        <v>408</v>
-      </c>
-      <c r="E12" s="10" t="s">
+      <c r="L24" s="22"/>
+    </row>
+    <row r="25" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B25" s="56"/>
+      <c r="C25" s="53" t="s">
+        <v>450</v>
+      </c>
+      <c r="D25" s="57" t="s">
+        <v>451</v>
+      </c>
+      <c r="E25" s="55" t="s">
+        <v>452</v>
+      </c>
+      <c r="F25" s="45" t="s">
+        <v>453</v>
+      </c>
+      <c r="G25" s="44" t="s">
         <v>409</v>
       </c>
-      <c r="F12" s="10" t="s">
-        <v>410</v>
-      </c>
-      <c r="G12" s="10" t="s">
+      <c r="H25" s="45" t="s">
+        <v>502</v>
+      </c>
+      <c r="I25" s="30" t="s">
         <v>479</v>
       </c>
-      <c r="H12" s="10" t="s">
-        <v>480</v>
-      </c>
-      <c r="I12" s="10" t="s">
-        <v>481</v>
-      </c>
-      <c r="J12" s="10" t="s">
-        <v>390</v>
-      </c>
-      <c r="K12" s="10"/>
-    </row>
-    <row r="13" spans="2:11" x14ac:dyDescent="0.45">
-      <c r="B13" s="10" t="s">
-        <v>411</v>
-      </c>
-      <c r="C13" s="10" t="s">
-        <v>412</v>
-      </c>
-      <c r="D13" s="10" t="s">
-        <v>413</v>
-      </c>
-      <c r="E13" s="10" t="s">
-        <v>414</v>
-      </c>
-      <c r="F13" s="10" t="s">
-        <v>415</v>
-      </c>
-      <c r="G13" s="10" t="s">
-        <v>482</v>
-      </c>
-      <c r="H13" s="10" t="s">
-        <v>483</v>
-      </c>
-      <c r="I13" s="10" t="s">
-        <v>484</v>
-      </c>
-      <c r="J13" s="10" t="s">
-        <v>390</v>
-      </c>
-      <c r="K13" s="10"/>
-    </row>
-    <row r="14" spans="2:11" x14ac:dyDescent="0.45">
-      <c r="B14" s="10"/>
-      <c r="C14" s="10"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="10"/>
-      <c r="G14" s="10"/>
-      <c r="H14" s="10"/>
-      <c r="I14" s="10"/>
-      <c r="J14" s="10"/>
-      <c r="K14" s="10"/>
-    </row>
-    <row r="15" spans="2:11" x14ac:dyDescent="0.45">
-      <c r="B15" s="10" t="s">
-        <v>416</v>
-      </c>
-      <c r="C15" s="10" t="s">
-        <v>417</v>
-      </c>
-      <c r="D15" s="10" t="s">
-        <v>418</v>
-      </c>
-      <c r="E15" s="10" t="s">
-        <v>419</v>
-      </c>
-      <c r="F15" s="10" t="s">
-        <v>420</v>
-      </c>
-      <c r="G15" s="10" t="s">
-        <v>485</v>
-      </c>
-      <c r="H15" s="10" t="s">
-        <v>486</v>
-      </c>
-      <c r="I15" s="10" t="s">
-        <v>487</v>
-      </c>
-      <c r="J15" s="10" t="s">
-        <v>400</v>
-      </c>
-      <c r="K15" s="10"/>
-    </row>
-    <row r="16" spans="2:11" x14ac:dyDescent="0.45">
-      <c r="B16" s="10" t="s">
-        <v>421</v>
-      </c>
-      <c r="C16" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="D16" s="10" t="s">
-        <v>423</v>
-      </c>
-      <c r="E16" s="10" t="s">
-        <v>424</v>
-      </c>
-      <c r="F16" s="10" t="s">
-        <v>425</v>
-      </c>
-      <c r="G16" s="10" t="s">
-        <v>488</v>
-      </c>
-      <c r="H16" s="10" t="s">
-        <v>489</v>
-      </c>
-      <c r="I16" s="10" t="s">
-        <v>490</v>
-      </c>
-      <c r="J16" s="10" t="s">
-        <v>400</v>
-      </c>
-      <c r="K16" s="10"/>
-    </row>
-    <row r="17" spans="2:11" x14ac:dyDescent="0.45">
-      <c r="B17" s="10" t="s">
-        <v>426</v>
-      </c>
-      <c r="C17" s="10" t="s">
-        <v>427</v>
-      </c>
-      <c r="D17" s="10" t="s">
-        <v>428</v>
-      </c>
-      <c r="E17" s="10" t="s">
-        <v>409</v>
-      </c>
-      <c r="F17" s="10" t="s">
-        <v>429</v>
-      </c>
-      <c r="G17" s="10" t="s">
-        <v>491</v>
-      </c>
-      <c r="H17" s="10" t="s">
-        <v>492</v>
-      </c>
-      <c r="I17" s="10" t="s">
-        <v>493</v>
-      </c>
-      <c r="J17" s="10" t="s">
-        <v>400</v>
-      </c>
-      <c r="K17" s="10"/>
-    </row>
-    <row r="18" spans="2:11" x14ac:dyDescent="0.45">
-      <c r="B18" s="10" t="s">
-        <v>430</v>
-      </c>
-      <c r="C18" s="10" t="s">
-        <v>431</v>
-      </c>
-      <c r="D18" s="10" t="s">
-        <v>432</v>
-      </c>
-      <c r="E18" s="10" t="s">
-        <v>409</v>
-      </c>
-      <c r="F18" s="10" t="s">
-        <v>433</v>
-      </c>
-      <c r="G18" s="10" t="s">
-        <v>494</v>
-      </c>
-      <c r="H18" s="10" t="s">
-        <v>495</v>
-      </c>
-      <c r="I18" s="10" t="s">
-        <v>463</v>
-      </c>
-      <c r="J18" s="10" t="s">
-        <v>400</v>
-      </c>
-      <c r="K18" s="10"/>
-    </row>
-    <row r="19" spans="2:11" x14ac:dyDescent="0.45">
-      <c r="B19" s="10" t="s">
-        <v>434</v>
-      </c>
-      <c r="C19" s="10" t="s">
-        <v>435</v>
-      </c>
-      <c r="D19" s="10" t="s">
-        <v>436</v>
-      </c>
-      <c r="E19" s="10" t="s">
-        <v>437</v>
-      </c>
-      <c r="F19" s="10" t="s">
-        <v>438</v>
-      </c>
-      <c r="G19" s="10" t="s">
-        <v>496</v>
-      </c>
-      <c r="H19" s="10" t="s">
-        <v>497</v>
-      </c>
-      <c r="I19" s="10" t="s">
-        <v>478</v>
-      </c>
-      <c r="J19" s="10" t="s">
-        <v>400</v>
-      </c>
-      <c r="K19" s="10"/>
-    </row>
-    <row r="20" spans="2:11" x14ac:dyDescent="0.45">
-      <c r="B20" s="10" t="s">
-        <v>439</v>
-      </c>
-      <c r="C20" s="10" t="s">
-        <v>440</v>
-      </c>
-      <c r="D20" s="10" t="s">
-        <v>441</v>
-      </c>
-      <c r="E20" s="10" t="s">
-        <v>409</v>
-      </c>
-      <c r="F20" s="10" t="s">
-        <v>410</v>
-      </c>
-      <c r="G20" s="10" t="s">
-        <v>498</v>
-      </c>
-      <c r="H20" s="10" t="s">
-        <v>480</v>
-      </c>
-      <c r="I20" s="10" t="s">
-        <v>463</v>
-      </c>
-      <c r="J20" s="10" t="s">
-        <v>390</v>
-      </c>
-      <c r="K20" s="10"/>
-    </row>
-    <row r="21" spans="2:11" x14ac:dyDescent="0.45">
-      <c r="B21" s="10" t="s">
-        <v>442</v>
-      </c>
-      <c r="C21" s="10" t="s">
-        <v>443</v>
-      </c>
-      <c r="D21" s="10" t="s">
-        <v>444</v>
-      </c>
-      <c r="E21" s="10" t="s">
-        <v>445</v>
-      </c>
-      <c r="F21" s="10" t="s">
-        <v>446</v>
-      </c>
-      <c r="G21" s="10" t="s">
-        <v>499</v>
-      </c>
-      <c r="H21" s="10" t="s">
-        <v>483</v>
-      </c>
-      <c r="I21" s="10" t="s">
-        <v>500</v>
-      </c>
-      <c r="J21" s="10" t="s">
-        <v>390</v>
-      </c>
-      <c r="K21" s="10"/>
-    </row>
-    <row r="22" spans="2:11" x14ac:dyDescent="0.45">
-      <c r="B22" s="10"/>
-      <c r="C22" s="10"/>
-      <c r="D22" s="10"/>
-      <c r="E22" s="10"/>
-      <c r="F22" s="10"/>
-      <c r="G22" s="10"/>
-      <c r="H22" s="10"/>
-      <c r="I22" s="10"/>
-      <c r="J22" s="10"/>
-      <c r="K22" s="10"/>
-    </row>
-    <row r="23" spans="2:11" x14ac:dyDescent="0.45">
-      <c r="B23" s="10" t="s">
-        <v>447</v>
-      </c>
-      <c r="C23" s="10" t="s">
-        <v>448</v>
-      </c>
-      <c r="D23" s="10" t="s">
-        <v>449</v>
-      </c>
-      <c r="E23" s="10" t="s">
-        <v>409</v>
-      </c>
-      <c r="F23" s="10" t="s">
-        <v>450</v>
-      </c>
-      <c r="G23" s="10" t="s">
-        <v>501</v>
-      </c>
-      <c r="H23" s="10" t="s">
-        <v>502</v>
-      </c>
-      <c r="I23" s="10" t="s">
+      <c r="J25" s="30" t="s">
         <v>503</v>
       </c>
-      <c r="J23" s="10" t="s">
-        <v>400</v>
-      </c>
-      <c r="K23" s="10"/>
-    </row>
-    <row r="24" spans="2:11" x14ac:dyDescent="0.45">
-      <c r="B24" s="10" t="s">
-        <v>451</v>
-      </c>
-      <c r="C24" s="10" t="s">
-        <v>452</v>
-      </c>
-      <c r="D24" s="10" t="s">
-        <v>453</v>
-      </c>
-      <c r="E24" s="10" t="s">
-        <v>454</v>
-      </c>
-      <c r="F24" s="10" t="s">
-        <v>410</v>
-      </c>
-      <c r="G24" s="10" t="s">
-        <v>504</v>
-      </c>
-      <c r="H24" s="10" t="s">
-        <v>480</v>
-      </c>
-      <c r="I24" s="10" t="s">
-        <v>505</v>
-      </c>
-      <c r="J24" s="10" t="s">
-        <v>390</v>
-      </c>
-      <c r="K24" s="10"/>
+      <c r="K25" s="30" t="s">
+        <v>389</v>
+      </c>
+      <c r="L25" s="30"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B2:K2"/>
-  </mergeCells>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
